--- a/output/filme_datenbank.xlsx
+++ b/output/filme_datenbank.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L206"/>
+  <dimension ref="A1:L207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4004,298 +4004,298 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="43" customHeight="1">
+    <row r="74" ht="69" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Kein Wort</t>
+          <t>Kick It Like Beckham</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Hanna Antonina Wojcik-Slak</t>
+          <t>Gurinder Chadha</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>3.09</v>
+        <v>3.48</v>
       </c>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="5" t="n">
-        <v>394</v>
+        <v>264737</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>22.06.2026</t>
+          <t>05.07.2026</t>
         </is>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>On a barren island, a mother and son confront years of silence and misunderstandings in writer-director Hanna Slak’s formidable fourth feature film starring Maren Eggert, scored by Amélie Legrand, and shot by Claire Mathon.</t>
+          <t>Jess Bhamra, the daughter of a strict Indian couple in London, is not permitted to play organized soccer, even though she is 18. When Jess is playing for fun one day, her impressive skills are seen by Jules Paxton, who then convinces Jess to play for her semi-pro team. Jess uses elaborate excuses to hide her matches from her family while also dealing with her romantic feelings for her coach, Joe.</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/105548-000-A/kein-wort/</t>
+          <t>https://www.3sat.de/film/spielfilm/kick-it-like-beckham-100.html</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/not-a-word-2023/</t>
+          <t>https://letterboxd.com/film/bend-it-like-beckham/</t>
         </is>
       </c>
     </row>
     <row r="75" ht="43" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Mo Hayder: Ritualmord</t>
+          <t>Kein Wort</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>ZDF</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Hans Herbots</t>
+          <t>Hanna Antonina Wojcik-Slak</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="5" t="n">
-        <v>977</v>
+        <v>394</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>28.06.2026</t>
+          <t>22.06.2026</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>The discovery of a chopped-off hand in a Brussels canal forces Belgian police diver Kiki to face deep guilt from the past, her own and her country’s.  Based on the book ‘Ritual’ by Mo Hayder.</t>
+          <t>On a barren island, a mother and son confront years of silence and misunderstandings in writer-director Hanna Slak’s formidable fourth feature film starring Maren Eggert, scored by Amélie Legrand, and shot by Claire Mathon.</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/mo-hayder-ritualmord-movie-100</t>
+          <t>https://www.arte.tv/de/videos/105548-000-A/kein-wort/</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/ritual-2022/</t>
+          <t>https://letterboxd.com/film/not-a-word-2023/</t>
         </is>
       </c>
     </row>
     <row r="76" ht="43" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Footloose</t>
+          <t>Mo Hayder: Ritualmord</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ZDF</t>
         </is>
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Herbert Ross</t>
+          <t>Hans Herbots</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="5" t="n">
-        <v>233046</v>
+        <v>977</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>28.06.2026</t>
         </is>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>When teenager Ren and his family move from big-city Chicago to a small town in the West, he's in for a real case of culture shock after discovering he's living in a place where music and dancing are illegal.</t>
+          <t>The discovery of a chopped-off hand in a Brussels canal forces Belgian police diver Kiki to face deep guilt from the past, her own and her country’s.  Based on the book ‘Ritual’ by Mo Hayder.</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/footloose-104.html</t>
+          <t>https://www.zdf.de/filme/mo-hayder-ritualmord-movie-100</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/footloose/</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/ritual-2022/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="43" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Ferien auf Immenhof</t>
+          <t>Footloose</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>ARD</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Hermann Leitner</t>
+          <t>Herbert Ross</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="F77" s="4" t="n"/>
       <c r="G77" s="5" t="n">
-        <v>248</v>
+        <v>233046</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>21.06.2026</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>The pony hotel has just been opened, but so far no guests have arrived. Dick gets Ralf to design a brochure about the hotel. The girls and Ethelbert then lead the village children on horseback to Lübeck, where they all distribute the brochure - not knowing that Dalli has added some embellishments to the text.</t>
+          <t>When teenager Ren and his family move from big-city Chicago to a small town in the West, he's in for a real case of culture shock after discovering he's living in a place where music and dancing are illegal.</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS9wbGFuQVJEXzM1NmQyZDgzLWFmZmMtNDc3Zi05YTk4LTM5OGY0M2U3YzAzZF9nYW56ZVNlbmR1bmc</t>
+          <t>https://www.3sat.de/film/spielfilm/footloose-104.html</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/ferien-auf-immenhof/</t>
+          <t>https://letterboxd.com/film/footloose/</t>
         </is>
       </c>
     </row>
     <row r="78" ht="56" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Final Fantasy: Die Mächte in dir</t>
+          <t>Ferien auf Immenhof</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>ZDFneo</t>
+          <t>ARD</t>
         </is>
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Hironobu Sakaguchi</t>
+          <t>Hermann Leitner</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>2.67</v>
+        <v>3.36</v>
       </c>
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="5" t="n">
-        <v>33485</v>
+        <v>248</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>25.06.2026</t>
+          <t>21.06.2026</t>
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>Led by a strange dream, scientist Aki Ross struggles to collect the eight spirits in the hope of creating a force powerful enough to protect the planet. With the aid of the Deep Eyes Squadron and her mentor, Dr. Sid, Aki must save the Earth from its darkest hate and unleash the spirits within.</t>
+          <t>The pony hotel has just been opened, but so far no guests have arrived. Dick gets Ralf to design a brochure about the hotel. The girls and Ethelbert then lead the village children on horseback to Lübeck, where they all distribute the brochure - not knowing that Dalli has added some embellishments to the text.</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/animation/final-fantasy-die-maechte-in-dir-movie-100</t>
+          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS9wbGFuQVJEXzM1NmQyZDgzLWFmZmMtNDc3Zi05YTk4LTM5OGY0M2U3YzAzZF9nYW56ZVNlbmR1bmc</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/final-fantasy-the-spirits-within/</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/ferien-auf-immenhof/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="56" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Der weite Himmel</t>
+          <t>Final Fantasy: Die Mächte in dir</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ZDFneo</t>
         </is>
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Howard Hawks</t>
+          <t>Hironobu Sakaguchi</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="5" t="n">
-        <v>4525</v>
+        <v>33485</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>28.12.2025</t>
+          <t>25.06.2026</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>Two tough Kentucky mountaineers join a trading expedition from St. Louis up the Missouri River to trade whisky for furs with the Blackfoot Indians. They soon discover that there is much more than the elements to contend with.</t>
+          <t>Led by a strange dream, scientist Aki Ross struggles to collect the eight spirits in the hope of creating a force powerful enough to protect the planet. With the aid of the Deep Eyes Squadron and her mentor, Dr. Sid, Aki must save the Earth from its darkest hate and unleash the spirits within.</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/der-weite-himmel-100.html</t>
+          <t>https://www.zdf.de/animation/final-fantasy-die-maechte-in-dir-movie-100</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-big-sky/</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/final-fantasy-the-spirits-within/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="43" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Die Grundschullehrerin</t>
+          <t>Der weite Himmel</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4306,332 +4306,332 @@
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Hélène Angel</t>
+          <t>Howard Hawks</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="5" t="n">
-        <v>1411</v>
+        <v>4525</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>18.10.2025</t>
+          <t>28.12.2025</t>
         </is>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>Florence is a school teacher devoted to her students. When she encounters young Sacha, a child with problems, she will do everything she can to help him, even to the point of neglecting her own children, her own life, and of questioning her vocation. Little by little Florence realizes that learning has no age limit.</t>
+          <t>Two tough Kentucky mountaineers join a trading expedition from St. Louis up the Missouri River to trade whisky for furs with the Blackfoot Indians. They soon discover that there is much more than the elements to contend with.</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/die-grundschullehrerin-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/der-weite-himmel-100.html</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/elementary/</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/the-big-sky/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="56" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Lehrer kann jeder!</t>
+          <t>Die Grundschullehrerin</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ZDF</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Ingo Rasper</t>
+          <t>Hélène Angel</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>2.99</v>
+        <v>3.43</v>
       </c>
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="5" t="n">
-        <v>276</v>
+        <v>1411</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>16.05.2026</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>Richard lives apart from his wife. He is unemployed. His life is really not running smoothly right now. Rather by chance, he gets into conversation with the director of his daughter's school, who is desperately looking for teachers - which gives Richard an idea. He is a mathematician. And after all, everyone can become a teacher!</t>
+          <t>Florence is a school teacher devoted to her students. When she encounters young Sacha, a child with problems, she will do everything she can to help him, even to the point of neglecting her own children, her own life, and of questioning her vocation. Little by little Florence realizes that learning has no age limit.</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/lehrer-kann-jeder-movie-100</t>
+          <t>https://www.3sat.de/film/spielfilm/die-grundschullehrerin-100.html</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/lehrer-kann-jeder/</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="95" customHeight="1">
+          <t>https://letterboxd.com/film/elementary/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="69" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Kinder, Küche, Chaos</t>
+          <t>Lehrer kann jeder!</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>ZDF</t>
         </is>
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Isabelle Czajka</t>
+          <t>Ingo Rasper</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="5" t="n">
-        <v>654</v>
+        <v>276</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>13.03.2019</t>
+          <t>16.05.2026</t>
         </is>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>Juliette was simply not sure about coming to live in this residential suburb of the greater Paris metropolitan area. All the women here are in their forties, have children to raise, houses to keep and husbands who return home late at night.Today she has an appointment in Paris that is important for her career, but she also has to run errands and pick up the kids from school. During the course of her day, monopolized by petty, everyday tasks, Juliette can feel the noose of domestic obligations and household chores slowly tightening around her neck.</t>
+          <t>Richard lives apart from his wife. He is unemployed. His life is really not running smoothly right now. Rather by chance, he gets into conversation with the director of his daughter's school, who is desperately looking for teachers - which gives Richard an idea. He is a mathematician. And after all, everyone can become a teacher!</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/083838-000-A/kinder-kueche-chaos/</t>
+          <t>https://www.zdf.de/filme/lehrer-kann-jeder-movie-100</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/domestic-life/</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="30" customHeight="1">
+          <t>https://letterboxd.com/film/lehrer-kann-jeder/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="95" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Never Grow Old</t>
+          <t>Kinder, Küche, Chaos</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Ivan Kavanagh</t>
+          <t>Isabelle Czajka</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="F83" s="4" t="n"/>
       <c r="G83" s="5" t="n">
-        <v>2944</v>
+        <v>654</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>29.08.2025</t>
+          <t>13.03.2019</t>
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>An Irish undertaker profits when outlaws take over a peaceful town, but his own family come under threat as the death toll increases dramatically.</t>
+          <t>Juliette was simply not sure about coming to live in this residential suburb of the greater Paris metropolitan area. All the women here are in their forties, have children to raise, houses to keep and husbands who return home late at night.Today she has an appointment in Paris that is important for her career, but she also has to run errands and pick up the kids from school. During the course of her day, monopolized by petty, everyday tasks, Juliette can feel the noose of domestic obligations and household chores slowly tightening around her neck.</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/never-grow-old-100.html</t>
+          <t>https://www.arte.tv/de/videos/083838-000-A/kinder-kueche-chaos/</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/never-grow-old/</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/domestic-life/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Das Lehrerzimmer</t>
+          <t>Never Grow Old</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>ZDF</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>İlker Çatak</t>
+          <t>Ivan Kavanagh</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>3.77</v>
+        <v>3.18</v>
       </c>
       <c r="F84" s="4" t="n"/>
       <c r="G84" s="5" t="n">
-        <v>124759</v>
+        <v>2944</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>06.05.2026</t>
+          <t>29.08.2025</t>
         </is>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>When one of her students is suspected of theft, teacher Carla Nowak decides to get to the bottom of the matter. Caught between her ideals and the school system, the consequences of her actions threaten to break her.</t>
+          <t>An Irish undertaker profits when outlaws take over a peaceful town, but his own family come under threat as the death toll increases dramatically.</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/das-lehrerzimmer-movie-102</t>
+          <t>https://www.3sat.de/film/spielfilm/never-grow-old-100.html</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-teachers-lounge-2023/</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/never-grow-old/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="43" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Taxi Teheran</t>
+          <t>Das Lehrerzimmer</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>ZDF</t>
         </is>
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Jafar Panahi</t>
+          <t>İlker Çatak</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="F85" s="4" t="n"/>
       <c r="G85" s="5" t="n">
-        <v>39307</v>
+        <v>124759</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>14.02.2018</t>
+          <t>06.05.2026</t>
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>A yellow cab is driving through the vibrant and colourful streets of Tehran. Very diverse passengers enter the taxi, each candidly expressing their views while being interviewed by the driver who is no one else but the director Jafar Panahi himself. His camera placed on the dashboard of his mobile film studio captures the spirit of Iranian society through this comedic and dramatic drive…</t>
+          <t>When one of her students is suspected of theft, teacher Carla Nowak decides to get to the bottom of the matter. Caught between her ideals and the school system, the consequences of her actions threaten to break her.</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/071355-000-A/taxi-teheran/</t>
+          <t>https://www.zdf.de/filme/das-lehrerzimmer-movie-102</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/taxi-2015/</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="82" customHeight="1">
+          <t>https://letterboxd.com/film/the-teachers-lounge-2023/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="69" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Die Mitte der Welt</t>
+          <t>Taxi Teheran</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Jakob M. Erwa</t>
+          <t>Jafar Panahi</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>3.18</v>
+        <v>3.86</v>
       </c>
       <c r="F86" s="4" t="n"/>
       <c r="G86" s="5" t="n">
-        <v>10944</v>
+        <v>39307</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>14.02.2018</t>
         </is>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>A strange family: 17-year-old Phil lives with his mother and twin sister in an old mansion on the outskirts of town. When he returns from summer camp, the mood in the mansion has soured somehow. Phil doesn’t worry about it, hanging out with his best friend Kat instead. When he starts to feel attracted to a mysterious new student at school, Phil is plunged into emotional turmoil only exacerbated by the trouble at home.</t>
+          <t>A yellow cab is driving through the vibrant and colourful streets of Tehran. Very diverse passengers enter the taxi, each candidly expressing their views while being interviewed by the driver who is no one else but the director Jafar Panahi himself. His camera placed on the dashboard of his mobile film studio captures the spirit of Iranian society through this comedic and dramatic drive…</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/die-mitte-der-welt-100.html</t>
+          <t>https://www.arte.tv/de/videos/071355-000-A/taxi-teheran/</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/center-of-my-world/</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/taxi-2015/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="82" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Rogue Trader</t>
+          <t>Die Mitte der Welt</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4642,140 +4642,140 @@
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>James Dearden</t>
+          <t>Jakob M. Erwa</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>3.06</v>
+        <v>3.18</v>
       </c>
       <c r="F87" s="4" t="n"/>
       <c r="G87" s="5" t="n">
-        <v>2843</v>
+        <v>10944</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>11.10.2025</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>Rogue Trader tells the true story of Nick Leeson, an employee of Barings Bank who--after a successful trading run--ends up accumulating $1.4 billion in losses hidden in account #88888.</t>
+          <t>A strange family: 17-year-old Phil lives with his mother and twin sister in an old mansion on the outskirts of town. When he returns from summer camp, the mood in the mansion has soured somehow. Phil doesn’t worry about it, hanging out with his best friend Kat instead. When he starts to feel attracted to a mysterious new student at school, Phil is plunged into emotional turmoil only exacerbated by the trouble at home.</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/rogue-trader-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/die-mitte-der-welt-100.html</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/rogue-trader/</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/center-of-my-world/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="43" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>The Yards - Im Hinterhof der Macht</t>
+          <t>Rogue Trader</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>James Gray</t>
+          <t>James Dearden</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>3.49</v>
+        <v>3.06</v>
       </c>
       <c r="F88" s="4" t="n"/>
       <c r="G88" s="5" t="n">
-        <v>22654</v>
+        <v>2843</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>17.03.2026</t>
+          <t>11.10.2025</t>
         </is>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>In the rail yards of Queens, contractors repair and rebuild the city's subway cars. These contracts are lucrative, so graft and corruption are rife. When Leo Handler gets out of prison, he finds his aunt married to Frank Olchin, one of the big contractors; he's battling with a minority-owned firm for contracts.</t>
+          <t>Rogue Trader tells the true story of Nick Leeson, an employee of Barings Bank who--after a successful trading run--ends up accumulating $1.4 billion in losses hidden in account #88888.</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/130331-000-A/the-yards-im-hinterhof-der-macht/</t>
+          <t>https://www.3sat.de/film/spielfilm/rogue-trader-100.html</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-yards/</t>
+          <t>https://letterboxd.com/film/rogue-trader/</t>
         </is>
       </c>
     </row>
     <row r="89" ht="56" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Identität</t>
+          <t>The Yards - Im Hinterhof der Macht</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>James Mangold</t>
+          <t>James Gray</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>3.44</v>
+        <v>3.49</v>
       </c>
       <c r="F89" s="4" t="n"/>
       <c r="G89" s="5" t="n">
-        <v>222539</v>
+        <v>22654</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>11.05.2025</t>
+          <t>17.03.2026</t>
         </is>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>Complete strangers stranded at a remote desert motel during a raging storm soon find themselves the target of a deranged murderer. As their numbers thin out, the travelers begin to turn on each other, as each tries to figure out who the killer is.</t>
+          <t>In the rail yards of Queens, contractors repair and rebuild the city's subway cars. These contracts are lucrative, so graft and corruption are rife. When Leo Handler gets out of prison, he finds his aunt married to Frank Olchin, one of the big contractors; he's battling with a minority-owned firm for contracts.</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/identitaet-102.html</t>
+          <t>https://www.arte.tv/de/videos/130331-000-A/the-yards-im-hinterhof-der-macht/</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/identity/</t>
+          <t>https://letterboxd.com/film/the-yards/</t>
         </is>
       </c>
     </row>
     <row r="90" ht="56" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Das Piano</t>
+          <t>Identität</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4786,44 +4786,44 @@
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Jane Campion</t>
+          <t>James Mangold</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>3.84</v>
+        <v>3.44</v>
       </c>
       <c r="F90" s="4" t="n"/>
       <c r="G90" s="5" t="n">
-        <v>133501</v>
+        <v>222539</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>13.09.2025</t>
+          <t>11.05.2025</t>
         </is>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
-          <t>When an arranged marriage brings Ada and her spirited daughter to the wilderness of nineteenth-century New Zealand, she finds herself locked in a battle of wills with both her controlling husband and a rugged frontiersman to whom she develops a forbidden attraction.</t>
+          <t>Complete strangers stranded at a remote desert motel during a raging storm soon find themselves the target of a deranged murderer. As their numbers thin out, the travelers begin to turn on each other, as each tries to figure out who the killer is.</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/das-piano-102.html</t>
+          <t>https://www.3sat.de/film/spielfilm/identitaet-102.html</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-piano/</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="30" customHeight="1">
+          <t>https://letterboxd.com/film/identity/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="56" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Eine Frau mit berauschenden Talenten</t>
+          <t>Das Piano</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4834,44 +4834,44 @@
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Jean-Paul Salomé</t>
+          <t>Jane Campion</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>3.12</v>
+        <v>3.84</v>
       </c>
       <c r="F91" s="4" t="n"/>
       <c r="G91" s="5" t="n">
-        <v>5712</v>
+        <v>133501</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>16.08.2025</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>A translator working for the police gets involved in the other side of drug dealing.</t>
+          <t>When an arranged marriage brings Ada and her spirited daughter to the wilderness of nineteenth-century New Zealand, she finds herself locked in a battle of wills with both her controlling husband and a rugged frontiersman to whom she develops a forbidden attraction.</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/eine-frau-mit-berauschenden-talenten-104.html</t>
+          <t>https://www.3sat.de/film/spielfilm/das-piano-102.html</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/mama-weed/</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/the-piano/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>The Nightingale - Schrei nach Rache</t>
+          <t>Eine Frau mit berauschenden Talenten</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4882,44 +4882,44 @@
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Jennifer Kent</t>
+          <t>Jean-Paul Salomé</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>3.73</v>
+        <v>3.12</v>
       </c>
       <c r="F92" s="4" t="n"/>
       <c r="G92" s="5" t="n">
-        <v>77718</v>
+        <v>5712</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>18.05.2025</t>
+          <t>16.08.2025</t>
         </is>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>In 1825, Clare, a 21-year-old Irish convict, chases a British soldier through the rugged Tasmanian wilderness, bent on revenge for a terrible act of violence he committed against her family. She enlists the services of an Aboriginal tracker who is also marked by trauma from his own violence-filled past.</t>
+          <t>A translator working for the police gets involved in the other side of drug dealing.</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/the-nightingale---schrei-nach-rache-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/eine-frau-mit-berauschenden-talenten-104.html</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-nightingale-2018/</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/mama-weed/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="56" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Stolz und Vorurteil</t>
+          <t>The Nightingale - Schrei nach Rache</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4930,44 +4930,44 @@
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Joe Wright</t>
+          <t>Jennifer Kent</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>4.14</v>
+        <v>3.73</v>
       </c>
       <c r="F93" s="4" t="n"/>
       <c r="G93" s="5" t="n">
-        <v>2167946</v>
+        <v>77718</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>19.10.2025</t>
+          <t>18.05.2025</t>
         </is>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>A story of love and life among the landed English gentry during the Georgian era. Mr. Bennet is a gentleman living in Hertfordshire with his overbearing wife and five daughters, but if he dies their house will be inherited by a distant cousin whom they have never met, so the family's future happiness and security is dependent on the daughters making good marriages.</t>
+          <t>In 1825, Clare, a 21-year-old Irish convict, chases a British soldier through the rugged Tasmanian wilderness, bent on revenge for a terrible act of violence he committed against her family. She enlists the services of an Aboriginal tracker who is also marked by trauma from his own violence-filled past.</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/stolz-und-vorurteil-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/the-nightingale---schrei-nach-rache-100.html</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/pride-prejudice/</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/the-nightingale-2018/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="69" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Macbeth</t>
+          <t>Stolz und Vorurteil</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4978,44 +4978,44 @@
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Joel Coen</t>
+          <t>Joe Wright</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>3.79</v>
+        <v>4.14</v>
       </c>
       <c r="F94" s="4" t="n"/>
       <c r="G94" s="5" t="n">
-        <v>197264</v>
+        <v>2167946</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>09.05.2026</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
-          <t>Macbeth, the Thane of Glamis, receives a prophecy from a trio of witches that one day he will become King of Scotland. Consumed by ambition and spurred to action by his wife, Macbeth murders his king and takes the throne for himself.</t>
+          <t>A story of love and life among the landed English gentry during the Georgian era. Mr. Bennet is a gentleman living in Hertfordshire with his overbearing wife and five daughters, but if he dies their house will be inherited by a distant cousin whom they have never met, so the family's future happiness and security is dependent on the daughters making good marriages.</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/macbeth-110.html</t>
+          <t>https://www.3sat.de/film/spielfilm/stolz-und-vorurteil-100.html</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-tragedy-of-macbeth/</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/pride-prejudice/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="43" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Im Netz der Gewalt</t>
+          <t>Macbeth</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5026,44 +5026,44 @@
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Joel Souza</t>
+          <t>Joel Coen</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>3.16</v>
+        <v>3.79</v>
       </c>
       <c r="F95" s="4" t="n"/>
       <c r="G95" s="5" t="n">
-        <v>2781</v>
+        <v>197264</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>09.05.2026</t>
         </is>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>One memorable night in the life of veteran patrol officer Ray Mandel and his trainee, ambitious rookie cop Nick Holland in the LAPD's Olympic Division. With two cop killers on the loose and hunting for more targets, Mandel and Holland must contend with a city about to boil over, as well as Jack VanZandt, an unhinged rogue cop out for payback running wild in their patrol zone.</t>
+          <t>Macbeth, the Thane of Glamis, receives a prophecy from a trio of witches that one day he will become King of Scotland. Consumed by ambition and spurred to action by his wife, Macbeth murders his king and takes the throne for himself.</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/im-netz-der-gewalt-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/macbeth-110.html</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/crown-vic/</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/the-tragedy-of-macbeth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="69" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Saturday Night Fever - Nur Samstag Nacht</t>
+          <t>Im Netz der Gewalt</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5074,44 +5074,44 @@
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>John Badham</t>
+          <t>Joel Souza</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="F96" s="4" t="n"/>
       <c r="G96" s="5" t="n">
-        <v>167889</v>
+        <v>2781</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>14.03.2025</t>
         </is>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t>Tony spends his Saturdays at a disco where his stylish moves raise his popularity among the patrons. But his life outside the disco is not easy and things change when he gets attracted to Stephanie.</t>
+          <t>One memorable night in the life of veteran patrol officer Ray Mandel and his trainee, ambitious rookie cop Nick Holland in the LAPD's Olympic Division. With two cop killers on the loose and hunting for more targets, Mandel and Holland must contend with a city about to boil over, as well as Jack VanZandt, an unhinged rogue cop out for payback running wild in their patrol zone.</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/saturday-night-fever---nur-samstag-nacht-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/im-netz-der-gewalt-100.html</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/saturday-night-fever/</t>
+          <t>https://letterboxd.com/film/crown-vic/</t>
         </is>
       </c>
     </row>
     <row r="97" ht="43" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Die Klapperschlange</t>
+          <t>Saturday Night Fever - Nur Samstag Nacht</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5122,188 +5122,188 @@
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>John Carpenter</t>
+          <t>John Badham</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>3.63</v>
+        <v>3.21</v>
       </c>
       <c r="F97" s="4" t="n"/>
       <c r="G97" s="5" t="n">
-        <v>273187</v>
+        <v>167889</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>17.10.2025</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>In a world ravaged by crime, the entire island of Manhattan has been converted into a walled prison where brutal prisoners roam free. After the US president crash-lands inside, war hero Snake Plissken has 24 hours to bring him back.</t>
+          <t>Tony spends his Saturdays at a disco where his stylish moves raise his popularity among the patrons. But his life outside the disco is not easy and things change when he gets attracted to Stephanie.</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/die-klapperschlange-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/saturday-night-fever---nur-samstag-nacht-100.html</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/escape-from-new-york/</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="30" customHeight="1">
+          <t>https://letterboxd.com/film/saturday-night-fever/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="43" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Die Spur der Knochen</t>
+          <t>Die Klapperschlange</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>ZDF</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Jorge Dorado</t>
+          <t>John Carpenter</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>2.52</v>
+        <v>3.63</v>
       </c>
       <c r="F98" s="4" t="n"/>
       <c r="G98" s="5" t="n">
-        <v>2189</v>
+        <v>273187</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>01.06.2026</t>
+          <t>17.10.2025</t>
         </is>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
-          <t>Mario, a worker in "lost and found" department, finds a suitcase with a dead baby inside.</t>
+          <t>In a world ravaged by crime, the entire island of Manhattan has been converted into a walled prison where brutal prisoners roam free. After the US president crash-lands inside, war hero Snake Plissken has 24 hours to bring him back.</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/die-spur-der-knochen-movie-100</t>
+          <t>https://www.3sat.de/film/spielfilm/die-klapperschlange-100.html</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/lost-found-2022/</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/escape-from-new-york/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="30" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Jakobs Ross</t>
+          <t>Die Spur der Knochen</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>ZDF</t>
         </is>
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Katalin Gödrös</t>
+          <t>Jorge Dorado</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>3.31</v>
+        <v>2.52</v>
       </c>
       <c r="F99" s="4" t="n"/>
       <c r="G99" s="5" t="n">
-        <v>282</v>
+        <v>2189</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>01.06.2026</t>
         </is>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>The musically highly gifted maid Elsie, who longs for a career as a musician, is forced into marriage with Jacob, a young stable boy who dreams of owning his own horse. Both have to learn that they can only escape their lack of opportunities if they team up.</t>
+          <t>Mario, a worker in "lost and found" department, finds a suitcase with a dead baby inside.</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/110971-000-A/jakobs-ross/</t>
+          <t>https://www.zdf.de/filme/die-spur-der-knochen-movie-100</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/songs-within/</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="30" customHeight="1">
+          <t>https://letterboxd.com/film/lost-found-2022/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="56" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Tödliches Kommando</t>
+          <t>Jakobs Ross</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Kathryn Bigelow</t>
+          <t>Katalin Gödrös</t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>3.75</v>
+        <v>3.31</v>
       </c>
       <c r="F100" s="4" t="n"/>
       <c r="G100" s="5" t="n">
-        <v>329651</v>
+        <v>282</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>23.01.2026</t>
+          <t>15.05.2026</t>
         </is>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>During the Iraq War, a Sergeant recently assigned to an army bomb squad is put at odds with his squad mates due to his maverick way of handling his work.</t>
+          <t>The musically highly gifted maid Elsie, who longs for a career as a musician, is forced into marriage with Jacob, a young stable boy who dreams of owning his own horse. Both have to learn that they can only escape their lack of opportunities if they team up.</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/toedliches-kommando-100.html</t>
+          <t>https://www.arte.tv/de/videos/110971-000-A/jakobs-ross/</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-hurt-locker/</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/songs-within/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="30" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Last Dance</t>
+          <t>Tödliches Kommando</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5314,44 +5314,44 @@
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Kelly Marcel</t>
+          <t>Kathryn Bigelow</t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="F101" s="4" t="n"/>
       <c r="G101" s="5" t="n">
-        <v>561312</v>
+        <v>329651</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>29.03.2026</t>
+          <t>23.01.2026</t>
         </is>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>Eddie and Venom are on the run. Hunted by both of their worlds and with the net closing in, the duo are forced into a devastating decision that will bring the curtains down on Venom and Eddie's last dance.</t>
+          <t>During the Iraq War, a Sergeant recently assigned to an army bomb squad is put at odds with his squad mates due to his maverick way of handling his work.</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/last-dance-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/toedliches-kommando-100.html</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/venom-the-last-dance/</t>
+          <t>https://letterboxd.com/film/the-hurt-locker/</t>
         </is>
       </c>
     </row>
     <row r="102" ht="43" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Der Mauretanier</t>
+          <t>Last Dance</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5362,44 +5362,44 @@
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Kevin Macdonald</t>
+          <t>Kelly Marcel</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>3.71</v>
+        <v>2.55</v>
       </c>
       <c r="F102" s="4" t="n"/>
       <c r="G102" s="5" t="n">
-        <v>60877</v>
+        <v>561312</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>06.02.2026</t>
+          <t>29.03.2026</t>
         </is>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>The true story of the Mauritanian Mohamedou Ould Slahi, who was held at the U.S military's Guantanamo Bay detention center without charges for over a decade and sought help from a defense attorney for his release.</t>
+          <t>Eddie and Venom are on the run. Hunted by both of their worlds and with the net closing in, the duo are forced into a devastating decision that will bring the curtains down on Venom and Eddie's last dance.</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/der-mauretanier-102.html</t>
+          <t>https://www.3sat.de/film/spielfilm/last-dance-100.html</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-mauritanian/</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/venom-the-last-dance/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="43" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Robin Hood - König der Diebe</t>
+          <t>Der Mauretanier</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5410,92 +5410,92 @@
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Kevin Reynolds</t>
+          <t>Kevin Macdonald</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>3.28</v>
+        <v>3.71</v>
       </c>
       <c r="F103" s="4" t="n"/>
       <c r="G103" s="5" t="n">
-        <v>109375</v>
+        <v>60877</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>25.12.2025</t>
+          <t>06.02.2026</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>Nobleman crusader Robin of Locksley breaks out of a Jerusalem prison with the help of Moorish fellow prisoner Azeem and travels back home to England. But upon arrival he discovers his dead father in the ruins of his family estate, killed by the vicious sheriff of Nottingham, Robin and Azeem join forces with outlaws Little John and Will Scarlett to save the kingdom from the sheriff's villainy.</t>
+          <t>The true story of the Mauritanian Mohamedou Ould Slahi, who was held at the U.S military's Guantanamo Bay detention center without charges for over a decade and sought help from a defense attorney for his release.</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/robin-hood---koenig-der-diebe-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/der-mauretanier-102.html</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/robin-hood-prince-of-thieves/</t>
+          <t>https://letterboxd.com/film/the-mauritanian/</t>
         </is>
       </c>
     </row>
     <row r="104" ht="69" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Die ewigen Brüste</t>
+          <t>Robin Hood - König der Diebe</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Kinuyo Tanaka</t>
+          <t>Kevin Reynolds</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="F104" s="4" t="n"/>
       <c r="G104" s="5" t="n">
-        <v>6226</v>
+        <v>109375</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>18.03.2026</t>
+          <t>25.12.2025</t>
         </is>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>
-          <t>Fumiko, mother of two children and wife of an unfaithful man, shares her family life with her budding vocation as a poet. The beginning of her successful literary career coincides with her divorce and her breast cancer diagnosis. In the last stage of her life, she meets a young journalist from Tokyo who wants to write a story on her life.</t>
+          <t>Nobleman crusader Robin of Locksley breaks out of a Jerusalem prison with the help of Moorish fellow prisoner Azeem and travels back home to England. But upon arrival he discovers his dead father in the ruins of his family estate, killed by the vicious sheriff of Nottingham, Robin and Azeem join forces with outlaws Little John and Will Scarlett to save the kingdom from the sheriff's villainy.</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/128684-000-A/die-ewigen-brueste/</t>
+          <t>https://www.3sat.de/film/spielfilm/robin-hood---koenig-der-diebe-100.html</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/forever-a-woman/</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/robin-hood-prince-of-thieves/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="69" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Die Nacht der Frauen</t>
+          <t>Die ewigen Brüste</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5510,40 +5510,40 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="F105" s="4" t="n"/>
       <c r="G105" s="5" t="n">
-        <v>4201</v>
+        <v>6226</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>18.03.2026</t>
         </is>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>In the wake of the 1956 Prostitution Prevention Law, a young woman recently released from one of Japan's new rehabilitation centers struggles to build a new life.</t>
+          <t>Fumiko, mother of two children and wife of an unfaithful man, shares her family life with her budding vocation as a poet. The beginning of her successful literary career coincides with her divorce and her breast cancer diagnosis. In the last stage of her life, she meets a young journalist from Tokyo who wants to write a story on her life.</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/128722-000-A/die-nacht-der-frauen/</t>
+          <t>https://www.arte.tv/de/videos/128684-000-A/die-ewigen-brueste/</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/girls-of-the-night/</t>
+          <t>https://letterboxd.com/film/forever-a-woman/</t>
         </is>
       </c>
     </row>
     <row r="106" ht="43" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Der Mond ist aufgegangen</t>
+          <t>Die Nacht der Frauen</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5558,14 +5558,14 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>3.77</v>
+        <v>3.92</v>
       </c>
       <c r="F106" s="4" t="n"/>
       <c r="G106" s="5" t="n">
-        <v>3561</v>
+        <v>4201</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
@@ -5574,24 +5574,24 @@
       </c>
       <c r="J106" s="6" t="inlineStr">
         <is>
-          <t>Mokichi Asai is a widowed father living in Nara with three daughters—Chizuru, Ayako, and Setsuko. The youngest, Setsuko, plays matchmaker for her older sisters, leading to humorous and awkward romantic entanglements.</t>
+          <t>In the wake of the 1956 Prostitution Prevention Law, a young woman recently released from one of Japan's new rehabilitation centers struggles to build a new life.</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/128726-000-A/der-mond-ist-aufgegangen/</t>
+          <t>https://www.arte.tv/de/videos/128722-000-A/die-nacht-der-frauen/</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-moon-has-risen/</t>
+          <t>https://letterboxd.com/film/girls-of-the-night/</t>
         </is>
       </c>
     </row>
     <row r="107" ht="43" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Fräulein Ogin</t>
+          <t>Der Mond ist aufgegangen</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5606,14 +5606,14 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>3.55</v>
+        <v>3.77</v>
       </c>
       <c r="F107" s="4" t="n"/>
       <c r="G107" s="5" t="n">
-        <v>2037</v>
+        <v>3561</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
@@ -5622,24 +5622,24 @@
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>A tea master and his daughter Ogin are both Christians in feudal Japan. Ogin falls in love with a married feudal prince who shares her faith. When the Shogun bans Christianity, the situation worsens.</t>
+          <t>Mokichi Asai is a widowed father living in Nara with three daughters—Chizuru, Ayako, and Setsuko. The youngest, Setsuko, plays matchmaker for her older sisters, leading to humorous and awkward romantic entanglements.</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/128721-000-A/fraeulein-ogin/</t>
+          <t>https://www.arte.tv/de/videos/128726-000-A/der-mond-ist-aufgegangen/</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/love-under-the-crucifix/</t>
+          <t>https://letterboxd.com/film/the-moon-has-risen/</t>
         </is>
       </c>
     </row>
     <row r="108" ht="43" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Die wandelnde Prinzessin</t>
+          <t>Fräulein Ogin</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5654,14 +5654,14 @@
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="F108" s="4" t="n"/>
       <c r="G108" s="5" t="n">
-        <v>1582</v>
+        <v>2037</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
@@ -5670,72 +5670,72 @@
       </c>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>Pu Zhe, younger brother of the Emperor of Manchukuo, marries Ryuko, daughter of an aristocratic family. To the surprise of all, a deep love between Pu Zhe and Ryuko develops and is put to the test when Japan loses the war.</t>
+          <t>A tea master and his daughter Ogin are both Christians in feudal Japan. Ogin falls in love with a married feudal prince who shares her faith. When the Shogun bans Christianity, the situation worsens.</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/128725-000-A/die-wandelnde-prinzessin/</t>
+          <t>https://www.arte.tv/de/videos/128721-000-A/fraeulein-ogin/</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-wandering-princess/</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/love-under-the-crucifix/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="43" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Das fliegende Klassenzimmer</t>
+          <t>Die wandelnde Prinzessin</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Kurt Hoffmann</t>
+          <t>Kinuyo Tanaka</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="F109" s="4" t="n"/>
       <c r="G109" s="5" t="n">
-        <v>396</v>
+        <v>1582</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>27.04.2025</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>The third form of a boarding school and the students of a neighboring school do not get along. Each side dreams up the craziest pranks to defeat the other. And when one day the high school students go as far as stealing the Gymnasium students’ essays and even burning them, daily school life really gets out of hand.</t>
+          <t>Pu Zhe, younger brother of the Emperor of Manchukuo, marries Ryuko, daughter of an aristocratic family. To the surprise of all, a deep love between Pu Zhe and Ryuko develops and is put to the test when Japan loses the war.</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/das-fliegende-klassenzimmer-106.html</t>
+          <t>https://www.arte.tv/de/videos/128725-000-A/die-wandelnde-prinzessin/</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-flying-classroom/</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/the-wandering-princess/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="56" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Nymphomaniac 1</t>
+          <t>Das fliegende Klassenzimmer</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5746,44 +5746,44 @@
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Lars von Trier</t>
+          <t>Kurt Hoffmann</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>3.51</v>
+        <v>3.56</v>
       </c>
       <c r="F110" s="4" t="n"/>
       <c r="G110" s="5" t="n">
-        <v>247396</v>
+        <v>396</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>08.01.2026</t>
+          <t>27.04.2025</t>
         </is>
       </c>
       <c r="J110" s="6" t="inlineStr">
         <is>
-          <t>A man named Seligman finds a fainted wounded woman in an alley and he brings her home. She tells him that her name is Joe and that she is nymphomaniac. Joe tells her life and sexual experiences with hundreds of men since she was a young teenager while Seligman tells about his hobbies, such as fly fishing, reading about Fibonacci numbers or listening to organ music.</t>
+          <t>The third form of a boarding school and the students of a neighboring school do not get along. Each side dreams up the craziest pranks to defeat the other. And when one day the high school students go as far as stealing the Gymnasium students’ essays and even burning them, daily school life really gets out of hand.</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/nymphomaniac-1-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/das-fliegende-klassenzimmer-106.html</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/nymphomaniac-volume-i/</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="30" customHeight="1">
+          <t>https://letterboxd.com/film/the-flying-classroom/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="69" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Nymphomaniac 2</t>
+          <t>Nymphomaniac 1</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5798,88 +5798,88 @@
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>3.33</v>
+        <v>3.51</v>
       </c>
       <c r="F111" s="4" t="n"/>
       <c r="G111" s="5" t="n">
-        <v>173365</v>
+        <v>247396</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>09.01.2026</t>
+          <t>08.01.2026</t>
         </is>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>The continuation of Joe's sexually dictated life delves into the darker aspects of her adult life and what led to her being in Seligman's care.</t>
+          <t>A man named Seligman finds a fainted wounded woman in an alley and he brings her home. She tells him that her name is Joe and that she is nymphomaniac. Joe tells her life and sexual experiences with hundreds of men since she was a young teenager while Seligman tells about his hobbies, such as fly fishing, reading about Fibonacci numbers or listening to organ music.</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/nymphomaniac-2-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/nymphomaniac-1-100.html</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/nymphomaniac-volume-ii/</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/nymphomaniac-volume-i/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="30" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Der inszenierte Mord</t>
+          <t>Nymphomaniac 2</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Laurent Heynemann</t>
+          <t>Lars von Trier</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>3.37</v>
+        <v>3.33</v>
       </c>
       <c r="F112" s="4" t="n"/>
       <c r="G112" s="5" t="n">
-        <v>791</v>
+        <v>173365</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>02.03.2026</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="J112" s="6" t="inlineStr">
         <is>
-          <t>"Hangar" is a new agency whose purpose is to carry out missions even too sensitive for the police or intelligence services. The agency must eliminate a German female terrorist by the name of Birgitt Haas. The murder is to be disguised as a crime of passion, so an agent must lure Birgitt into falling in love.</t>
+          <t>The continuation of Joe's sexually dictated life delves into the darker aspects of her adult life and what led to her being in Seligman's care.</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/127952-000-A/der-inszenierte-mord/</t>
+          <t>https://www.3sat.de/film/spielfilm/nymphomaniac-2-100.html</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/birgit-haas-must-be-killed/</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="95" customHeight="1">
+          <t>https://letterboxd.com/film/nymphomaniac-volume-ii/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="56" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Lach doch mal</t>
+          <t>Der inszenierte Mord</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5890,44 +5890,44 @@
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Leida Laius</t>
+          <t>Laurent Heynemann</t>
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>3.73</v>
+        <v>3.37</v>
       </c>
       <c r="F113" s="4" t="n"/>
       <c r="G113" s="5" t="n">
-        <v>730</v>
+        <v>791</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>10.06.2026</t>
+          <t>02.03.2026</t>
         </is>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>16-year-old Mari, raised without a mother by a drunkard father, is put in an orphanage which she immediately, though unsuccessfully, tries to flee from. The sensitive Mari finds it hard to adapt to the coarse manners and brutal games amongst the children. Only gradually does she develop a sense for the similarly difficult fates of her fellow sufferers, who have long forgotten how to cry. She even falls in love for the first time, not with her self-appointed “protector” Tauri, but with the rough-mannered Robi.</t>
+          <t>"Hangar" is a new agency whose purpose is to carry out missions even too sensitive for the police or intelligence services. The agency must eliminate a German female terrorist by the name of Birgitt Haas. The murder is to be disguised as a crime of passion, so an agent must lure Birgitt into falling in love.</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/132072-000-A/lach-doch-mal/</t>
+          <t>https://www.arte.tv/de/videos/127952-000-A/der-inszenierte-mord/</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/smile-at-last/</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="82" customHeight="1">
+          <t>https://letterboxd.com/film/birgit-haas-must-be-killed/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="95" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Intime Geständnisse</t>
+          <t>Lach doch mal</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5938,92 +5938,92 @@
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Liv Ullmann</t>
+          <t>Leida Laius</t>
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>3.57</v>
+        <v>3.73</v>
       </c>
       <c r="F114" s="4" t="n"/>
       <c r="G114" s="5" t="n">
-        <v>287</v>
+        <v>730</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>193</v>
+        <v>82</v>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>08.01.2026</t>
+          <t>10.06.2026</t>
         </is>
       </c>
       <c r="J114" s="6" t="inlineStr">
         <is>
-          <t>Five conversations frame a flawed marriage in this film written by Ingmar Bergman about his parents. Guilt-ridden wife Anna (Pernilla August) divulges an extramarital affair to a priest, her uncle Jacob (Max von Sydow). He presses her to confess her sins to her husband, Henrik. As the film moves back and forth in time, the notion of truth is tested. Tomas, the lover, and Henrik will find that Anna's confessions do not absolve anyone, and have the power to inflict more pain.</t>
+          <t>16-year-old Mari, raised without a mother by a drunkard father, is put in an orphanage which she immediately, though unsuccessfully, tries to flee from. The sensitive Mari finds it hard to adapt to the coarse manners and brutal games amongst the children. Only gradually does she develop a sense for the similarly difficult fates of her fellow sufferers, who have long forgotten how to cry. She even falls in love for the first time, not with her self-appointed “protector” Tauri, but with the rough-mannered Robi.</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/129335-000-A/intime-gestaendnisse/</t>
+          <t>https://www.arte.tv/de/videos/132072-000-A/lach-doch-mal/</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/private-confessions/</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/smile-at-last/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="82" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Pappa ante Portas</t>
+          <t>Intime Geständnisse</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Loriot</t>
+          <t>Liv Ullmann</t>
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>3.85</v>
+        <v>3.57</v>
       </c>
       <c r="F115" s="4" t="n"/>
       <c r="G115" s="5" t="n">
-        <v>6206</v>
+        <v>287</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>04.03.2025</t>
+          <t>08.01.2026</t>
         </is>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>Heinrich Lohse, a strict and highly efficient purchasing manager at a company bulk-orders 40 tons of mustard and enough typewriting paper for 40 years just to get discount. Heinrich's boss decides it’s time for him to retire early. Heinrich suddenly finds himself with nothing to do—except micromanage his household, much to the dismay of his wife Renate and their son Dieter</t>
+          <t>Five conversations frame a flawed marriage in this film written by Ingmar Bergman about his parents. Guilt-ridden wife Anna (Pernilla August) divulges an extramarital affair to a priest, her uncle Jacob (Max von Sydow). He presses her to confess her sins to her husband, Henrik. As the film moves back and forth in time, the notion of truth is tested. Tomas, the lover, and Henrik will find that Anna's confessions do not absolve anyone, and have the power to inflict more pain.</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/pappa-ante-portas-100.html</t>
+          <t>https://www.arte.tv/de/videos/129335-000-A/intime-gestaendnisse/</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/pappa-ante-portas/</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="82" customHeight="1">
+          <t>https://letterboxd.com/film/private-confessions/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="69" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Ödipussi</t>
+          <t>Pappa ante Portas</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -6038,14 +6038,14 @@
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>3.56</v>
+        <v>3.85</v>
       </c>
       <c r="F116" s="4" t="n"/>
       <c r="G116" s="5" t="n">
-        <v>4531</v>
+        <v>6206</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
@@ -6054,24 +6054,24 @@
       </c>
       <c r="J116" s="6" t="inlineStr">
         <is>
-          <t>Paul Winkelmann is the CEO of a successful business in Hamburg that he took over after the death of his father eight years ago. But he is still strongly dominated by his 78 year old mother who cares for him as a child, and who cannot understand why he took an apartment on his own after all these years. The real "problem" starts when Paul gets to know psychologist Margarethe Tietze whose relationship to her parents is also not so easy after all.</t>
+          <t>Heinrich Lohse, a strict and highly efficient purchasing manager at a company bulk-orders 40 tons of mustard and enough typewriting paper for 40 years just to get discount. Heinrich's boss decides it’s time for him to retire early. Heinrich suddenly finds himself with nothing to do—except micromanage his household, much to the dismay of his wife Renate and their son Dieter</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/oedipussi-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/pappa-ante-portas-100.html</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/odipussi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/pappa-ante-portas/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="82" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Curiosa - Die Kunst der Verführung</t>
+          <t>Ödipussi</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -6082,44 +6082,44 @@
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Lou Jeunet</t>
+          <t>Loriot</t>
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>2.68</v>
+        <v>3.56</v>
       </c>
       <c r="F117" s="4" t="n"/>
       <c r="G117" s="5" t="n">
-        <v>9411</v>
+        <v>4531</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>06.01.2026</t>
+          <t>04.03.2025</t>
         </is>
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>A passionate love story set against a backdrop of sexual freedom, loosely based on the relationship between 19th century authors Pierre Louÿs and Marie de Régnier.</t>
+          <t>Paul Winkelmann is the CEO of a successful business in Hamburg that he took over after the death of his father eight years ago. But he is still strongly dominated by his 78 year old mother who cares for him as a child, and who cannot understand why he took an apartment on his own after all these years. The real "problem" starts when Paul gets to know psychologist Margarethe Tietze whose relationship to her parents is also not so easy after all.</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/curiosa---die-kunst-der-verfuehrung-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/oedipussi-100.html</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/curiosa/</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="147" customHeight="1">
+          <t>https://letterboxd.com/film/odipussi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="43" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Im Rausch der Tiefe</t>
+          <t>Curiosa - Die Kunst der Verführung</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -6130,140 +6130,140 @@
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Luc Besson</t>
+          <t>Lou Jeunet</t>
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>3.79</v>
+        <v>2.68</v>
       </c>
       <c r="F118" s="4" t="n"/>
       <c r="G118" s="5" t="n">
-        <v>56681</v>
+        <v>9411</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>12.10.2025</t>
+          <t>06.01.2026</t>
         </is>
       </c>
       <c r="J118" s="6" t="inlineStr">
         <is>
-          <t>Two men answer the call of the ocean in this romantic fantasy-adventure.  Jacques and Enzo are a pair of friends who have been close since childhood, and who share a passion for the dangerous sport of free diving. Professional diver Jacques opted to follow in the footsteps of his father, who died at sea when Jacques was a boy; to the bewilderment of scientists, Jacques harbors a remarkable ability to adjust his heart rate and breathing pattern in the water, so that his vital signs more closely resemble that of dolphins than men.  As Enzo persuades a reluctant Jacques to compete against him in a free diving contest -- determining who can dive deeper and longer without scuba gear -- Jacques meets Johana, a beautiful insurance investigator from America, and he finds that he must choose between his love for her and his love of the sea.</t>
+          <t>A passionate love story set against a backdrop of sexual freedom, loosely based on the relationship between 19th century authors Pierre Louÿs and Marie de Régnier.</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/im-rausch-der-tiefe-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/curiosa---die-kunst-der-verfuehrung-100.html</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-big-blue/</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/curiosa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="147" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Das Mädchen deiner Träume</t>
+          <t>Im Rausch der Tiefe</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>ZDF</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Luke Eve</t>
+          <t>Luc Besson</t>
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>3.14</v>
+        <v>3.79</v>
       </c>
       <c r="F119" s="4" t="n"/>
       <c r="G119" s="5" t="n">
-        <v>2224</v>
+        <v>56681</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>22.06.2026</t>
+          <t>12.10.2025</t>
         </is>
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>An aspiring musician struggling with schizophrenia falls for a mysterious woman who may be all in his head. When she suddenly vanishes, he takes off on a cross-country journey across Australia to find her, forcing his long-suffering brother to chase after him.</t>
+          <t>Two men answer the call of the ocean in this romantic fantasy-adventure.  Jacques and Enzo are a pair of friends who have been close since childhood, and who share a passion for the dangerous sport of free diving. Professional diver Jacques opted to follow in the footsteps of his father, who died at sea when Jacques was a boy; to the bewilderment of scientists, Jacques harbors a remarkable ability to adjust his heart rate and breathing pattern in the water, so that his vital signs more closely resemble that of dolphins than men.  As Enzo persuades a reluctant Jacques to compete against him in a free diving contest -- determining who can dive deeper and longer without scuba gear -- Jacques meets Johana, a beautiful insurance investigator from America, and he finds that he must choose between his love for her and his love of the sea.</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/das-maedchen-deiner-traeume-movie-100</t>
+          <t>https://www.3sat.de/film/spielfilm/im-rausch-der-tiefe-100.html</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/i-met-a-girl/</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="95" customHeight="1">
+          <t>https://letterboxd.com/film/the-big-blue/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="56" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Träum was Schönes</t>
+          <t>Das Mädchen deiner Träume</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>ZDF</t>
         </is>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Marco Bellocchio</t>
+          <t>Luke Eve</t>
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="F120" s="4" t="n"/>
       <c r="G120" s="5" t="n">
-        <v>2285</v>
+        <v>2224</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>07.01.2026</t>
+          <t>22.06.2026</t>
         </is>
       </c>
       <c r="J120" s="6" t="inlineStr">
         <is>
-          <t>Turin, 1969. Nine-year-old Massimo’s idyllic childhood is shattered by the mysterious death of his mother. The young boy refuses to accept this brutal loss, even if the priest says she is now in Heaven. Years later in the 90s, adult Massimo has become an accomplished journalist. After reporting on the war in Sarajevo, he begins to suffer from panic attacks. As he prepares to sell his parents’ apartment, Massimo is forced to relive his traumatic past. Compassionate doctor Elisa could help tormented Massimo open up and confront his childhood wounds…</t>
+          <t>An aspiring musician struggling with schizophrenia falls for a mysterious woman who may be all in his head. When she suddenly vanishes, he takes off on a cross-country journey across Australia to find her, forcing his long-suffering brother to chase after him.</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/118164-000-A/traeum-was-schoenes/</t>
+          <t>https://www.zdf.de/filme/das-maedchen-deiner-traeume-movie-100</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/sweet-dreams-2016/</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/i-met-a-girl/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="95" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Schlaf, mein Kindlein</t>
+          <t>Träum was Schönes</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6274,258 +6274,258 @@
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Margo Harkin</t>
+          <t>Marco Bellocchio</t>
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="F121" s="4" t="n"/>
       <c r="G121" s="5" t="n">
-        <v>298</v>
+        <v>2285</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>29.05.2026</t>
+          <t>07.01.2026</t>
         </is>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>1980s Derry: Goretti Friel, one of a spirited group of teenage friends, meets Ciarán at her Irish language class, and romance blossoms. When he is arrested and imprisoned by the British army, Goretti is dismayed to find herself pregnant. Left to deal with the crisis alone, she is tormented by the conflicts of her growing belly and the influence of a Catholic upbringing.</t>
+          <t>Turin, 1969. Nine-year-old Massimo’s idyllic childhood is shattered by the mysterious death of his mother. The young boy refuses to accept this brutal loss, even if the priest says she is now in Heaven. Years later in the 90s, adult Massimo has become an accomplished journalist. After reporting on the war in Sarajevo, he begins to suffer from panic attacks. As he prepares to sell his parents’ apartment, Massimo is forced to relive his traumatic past. Compassionate doctor Elisa could help tormented Massimo open up and confront his childhood wounds…</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/131538-000-A/schlaf-mein-kindlein/</t>
+          <t>https://www.arte.tv/de/videos/118164-000-A/traeum-was-schoenes/</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/hush-a-bye-baby/</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/sweet-dreams-2016/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="69" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Mein Ende. Dein Anfang.</t>
+          <t>Schlaf, mein Kindlein</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Mariko Minoguchi</t>
+          <t>Margo Harkin</t>
         </is>
       </c>
       <c r="E122" s="3" t="n">
-        <v>3.24</v>
+        <v>3.42</v>
       </c>
       <c r="F122" s="4" t="n"/>
       <c r="G122" s="5" t="n">
-        <v>891</v>
+        <v>298</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>08.03.2025</t>
+          <t>29.05.2026</t>
         </is>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t>The fate of Nora, a supermarket cashier who lives happily with her boyfriend Aron, and that of Natan, a loving father who works as a night watchman, cross paths when misfortune turns their lives upside down.</t>
+          <t>1980s Derry: Goretti Friel, one of a spirited group of teenage friends, meets Ciarán at her Irish language class, and romance blossoms. When he is arrested and imprisoned by the British army, Goretti is dismayed to find herself pregnant. Left to deal with the crisis alone, she is tormented by the conflicts of her growing belly and the influence of a Catholic upbringing.</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/mein-ende-dein-anfang-104.html</t>
+          <t>https://www.arte.tv/de/videos/131538-000-A/schlaf-mein-kindlein/</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/relativity-2019/</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="30" customHeight="1">
+          <t>https://letterboxd.com/film/hush-a-bye-baby/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="43" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Schock</t>
+          <t>Mein Ende. Dein Anfang.</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Mario Bava</t>
+          <t>Mariko Minoguchi</t>
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="F123" s="4" t="n"/>
       <c r="G123" s="5" t="n">
-        <v>12091</v>
+        <v>891</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>07.06.2026</t>
+          <t>08.03.2025</t>
         </is>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>A couple is terrorized in their new house haunted by the vengeful ghost of the woman's former husband who possesses her young son.</t>
+          <t>The fate of Nora, a supermarket cashier who lives happily with her boyfriend Aron, and that of Natan, a loving father who works as a night watchman, cross paths when misfortune turns their lives upside down.</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/100907-000-A/schock/</t>
+          <t>https://www.3sat.de/film/spielfilm/mein-ende-dein-anfang-104.html</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/shock-1977/</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/relativity-2019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="30" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Zu guter Letzt</t>
+          <t>Schock</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Mark Pellington</t>
+          <t>Mario Bava</t>
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>3.21</v>
+        <v>3.32</v>
       </c>
       <c r="F124" s="4" t="n"/>
       <c r="G124" s="5" t="n">
-        <v>5466</v>
+        <v>12091</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>02.03.2025</t>
+          <t>07.06.2026</t>
         </is>
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t>A retired businesswoman – who tries to control everything around her – decides to write her own obituary. A young journalist takes up the task of finding out the truth, and the result is a life-altering friendship.</t>
+          <t>A couple is terrorized in their new house haunted by the vengeful ghost of the woman's former husband who possesses her young son.</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/zu-guter-letzt-100.html</t>
+          <t>https://www.arte.tv/de/videos/100907-000-A/schock/</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-last-word-2017/</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/shock-1977/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="43" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Mein Lotta-Leben – Alles Tschaka mit Alpaka!</t>
+          <t>Zu guter Letzt</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>ZDF-tivi</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Martina Plura</t>
+          <t>Mark Pellington</t>
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="F125" s="4" t="n"/>
       <c r="G125" s="5" t="n">
-        <v>215</v>
+        <v>5466</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>10.06.2026</t>
+          <t>02.03.2025</t>
         </is>
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>Lotta Petermann is looking forward to her first class trip. Finally without parents and with her best friends Amrum unsicher machen - that promises pure adventure! But Mama Sabine sabotages Lotta's plans and suggests Papa Rainer, of all people, to accompany her on the class trip - how embarrassing!</t>
+          <t>A retired businesswoman – who tries to control everything around her – decides to write her own obituary. A young journalist takes up the task of finding out the truth, and the result is a life-altering friendship.</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/mein-lotta-leben--alles-tschaka-mit-alpaka-movie-100</t>
+          <t>https://www.3sat.de/film/spielfilm/zu-guter-letzt-100.html</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/my-life-as-lotta-okey-dokey-alpaca/</t>
+          <t>https://letterboxd.com/film/the-last-word-2017/</t>
         </is>
       </c>
     </row>
     <row r="126" ht="56" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>BlackBerry - Klick einer Generation</t>
+          <t>Mein Lotta-Leben – Alles Tschaka mit Alpaka!</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>ZDF-tivi</t>
         </is>
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Matt Johnson</t>
+          <t>Martina Plura</t>
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>3.77</v>
+        <v>3.08</v>
       </c>
       <c r="F126" s="4" t="n"/>
       <c r="G126" s="5" t="n">
-        <v>266692</v>
+        <v>215</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
@@ -6534,216 +6534,216 @@
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>Two mismatched entrepreneurs – egghead innovator Mike Lazaridis and cut-throat businessman Jim Balsillie – joined forces in an endeavour that was to become a worldwide hit in little more than a decade. The story of the meteoric rise and catastrophic demise of the world's first smartphone.</t>
+          <t>Lotta Petermann is looking forward to her first class trip. Finally without parents and with her best friends Amrum unsicher machen - that promises pure adventure! But Mama Sabine sabotages Lotta's plans and suggests Papa Rainer, of all people, to accompany her on the class trip - how embarrassing!</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/129823-000-A/blackberry-klick-einer-generation/</t>
+          <t>https://www.zdf.de/filme/mein-lotta-leben--alles-tschaka-mit-alpaka-movie-100</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/blackberry-2023/</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/my-life-as-lotta-okey-dokey-alpaca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="56" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Die Wannseekonferenz</t>
+          <t>BlackBerry - Klick einer Generation</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>ZDF</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Matti Geschonneck</t>
+          <t>Matt Johnson</t>
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>3.48</v>
+        <v>3.77</v>
       </c>
       <c r="F127" s="4" t="n"/>
       <c r="G127" s="5" t="n">
-        <v>7886</v>
+        <v>266692</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>05.05.2026</t>
+          <t>10.06.2026</t>
         </is>
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>On January 20, 1942, the Wannsee Conference takes place in Berlin, a meeting that had only one item on the agenda: The Final Solution, the organization of the systematic mass murder of eleven million European Jews.</t>
+          <t>Two mismatched entrepreneurs – egghead innovator Mike Lazaridis and cut-throat businessman Jim Balsillie – joined forces in an endeavour that was to become a worldwide hit in little more than a decade. The story of the meteoric rise and catastrophic demise of the world's first smartphone.</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/die-wannseekonferenz-movie-100</t>
+          <t>https://www.arte.tv/de/videos/129823-000-A/blackberry-klick-einer-generation/</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-conference/</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="108" customHeight="1">
+          <t>https://letterboxd.com/film/blackberry-2023/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="43" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Die Saat</t>
+          <t>Die Wannseekonferenz</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ZDF</t>
         </is>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Mia Maariel Meyer</t>
+          <t>Matti Geschonneck</t>
         </is>
       </c>
       <c r="E128" s="3" t="n">
-        <v>3.21</v>
+        <v>3.48</v>
       </c>
       <c r="F128" s="4" t="n"/>
       <c r="G128" s="5" t="n">
-        <v>294</v>
+        <v>7886</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>24.05.2025</t>
+          <t>05.05.2026</t>
         </is>
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>Rainer toils by the sweat of his brow on a building site. His first job as site manager is his much-needed big break. Rising rents in the city have already forced him, his pregnant wife and 13-year-old daughter Doreen to move into a little house in the outskirts which needs renovating. At first, Doreen is not thrilled about her new life but then she meets her neighbour Mara, a girl whose parents are as rich as they are narrow-minded. Before long the new friends are playing with fire. Mara incites Doreen to play some nasty tricks and also entangles her in a theft.</t>
+          <t>On January 20, 1942, the Wannsee Conference takes place in Berlin, a meeting that had only one item on the agenda: The Final Solution, the organization of the systematic mass murder of eleven million European Jews.</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/die-saat-102.html</t>
+          <t>https://www.zdf.de/filme/die-wannseekonferenz-movie-100</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-seed-2021/</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/the-conference/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="108" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Papillon</t>
+          <t>Die Saat</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>ARD</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Michael Noer</t>
+          <t>Mia Maariel Meyer</t>
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>3.55</v>
+        <v>3.21</v>
       </c>
       <c r="F129" s="4" t="n"/>
       <c r="G129" s="5" t="n">
-        <v>72216</v>
+        <v>294</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>24.05.2025</t>
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>Henri “Papillon” Charrière, a safecracker from the Parisian underworld, is wrongfully convicted and sentenced to life imprisonment in the penal colony of French Guiana, where he forges a strong friendship with Louis Dega, a counterfeiter who needs his protection.</t>
+          <t>Rainer toils by the sweat of his brow on a building site. His first job as site manager is his much-needed big break. Rising rents in the city have already forced him, his pregnant wife and 13-year-old daughter Doreen to move into a little house in the outskirts which needs renovating. At first, Doreen is not thrilled about her new life but then she meets her neighbour Mara, a girl whose parents are as rich as they are narrow-minded. Before long the new friends are playing with fire. Mara incites Doreen to play some nasty tricks and also entangles her in a theft.</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS9wbGFuQVJEX2UzYjk0OTNiLWJkNmMtNGIwNi04YjQ1LWY5MmRkMzNlNjA5Ml9nYW56ZVNlbmR1bmc</t>
+          <t>https://www.3sat.de/film/spielfilm/die-saat-102.html</t>
         </is>
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/papillon-2017/</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/the-seed-2021/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="56" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Liebe 1962</t>
+          <t>Papillon</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>ARD</t>
         </is>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Michelangelo Antonioni</t>
+          <t>Michael Noer</t>
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>3.98</v>
+        <v>3.55</v>
       </c>
       <c r="F130" s="4" t="n"/>
       <c r="G130" s="5" t="n">
-        <v>60494</v>
+        <v>72216</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>29.06.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>Vittoria is a beautiful literary translator living in Rome. After splitting from her writer boyfriend, Riccardo, Vittoria meets Piero, a lively stockbroker, on the hectic floor of the Roman stock exchange. Though Vittoria and Piero begin a relationship, it is not one without difficulties, and their commitment to one another is tested during an eclipse.</t>
+          <t>Henri “Papillon” Charrière, a safecracker from the Parisian underworld, is wrongfully convicted and sentenced to life imprisonment in the penal colony of French Guiana, where he forges a strong friendship with Louis Dega, a counterfeiter who needs his protection.</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/002734-000-A/liebe-1962/</t>
+          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS9wbGFuQVJEX2UzYjk0OTNiLWJkNmMtNGIwNi04YjQ1LWY5MmRkMzNlNjA5Ml9nYW56ZVNlbmR1bmc</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/leclisse/</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/papillon-2017/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="69" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>All or Nothing</t>
+          <t>Liebe 1962</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6754,140 +6754,140 @@
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Mike Leigh</t>
+          <t>Michelangelo Antonioni</t>
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>3.89</v>
+        <v>3.98</v>
       </c>
       <c r="F131" s="4" t="n"/>
       <c r="G131" s="5" t="n">
-        <v>9080</v>
+        <v>60494</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>29.06.2026</t>
         </is>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>Penny works at a supermarket and Phil is a gentle taxi-driver. Penny’s love for Phil has run dry and they lead joyless lives with their two children, Rachel, a cleaner, and Rory, who is unemployed and aggressive.</t>
+          <t>Vittoria is a beautiful literary translator living in Rome. After splitting from her writer boyfriend, Riccardo, Vittoria meets Piero, a lively stockbroker, on the hectic floor of the Roman stock exchange. Though Vittoria and Piero begin a relationship, it is not one without difficulties, and their commitment to one another is tested during an eclipse.</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/044959-000-A/all-or-nothing/</t>
+          <t>https://www.arte.tv/de/videos/002734-000-A/liebe-1962/</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/all-or-nothing/</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="30" customHeight="1">
+          <t>https://letterboxd.com/film/leclisse/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="43" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Hautnah</t>
+          <t>All or Nothing</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Mike Nichols</t>
+          <t>Mike Leigh</t>
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>3.39</v>
+        <v>3.89</v>
       </c>
       <c r="F132" s="4" t="n"/>
       <c r="G132" s="5" t="n">
-        <v>432818</v>
+        <v>9080</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>04.07.2025</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>The relationships of two couples become complicated and deceitful when the man from one couple meets the woman of the other.</t>
+          <t>Penny works at a supermarket and Phil is a gentle taxi-driver. Penny’s love for Phil has run dry and they lead joyless lives with their two children, Rachel, a cleaner, and Rory, who is unemployed and aggressive.</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/hautnah-100.html</t>
+          <t>https://www.arte.tv/de/videos/044959-000-A/all-or-nothing/</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/closer/</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/all-or-nothing/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="30" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Doch das Böse gibt es nicht</t>
+          <t>Hautnah</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Mohammad Rasoulof</t>
+          <t>Mike Nichols</t>
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>3.8</v>
+        <v>3.39</v>
       </c>
       <c r="F133" s="4" t="n"/>
       <c r="G133" s="5" t="n">
-        <v>15861</v>
+        <v>432818</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>19.02.2024</t>
+          <t>04.07.2025</t>
         </is>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>Set against the backdrop of Iran's strict and oppressive legal system, this anthology film tells the stories of four men who each face a moral crisis when having to deal with death penalties.</t>
+          <t>The relationships of two couples become complicated and deceitful when the man from one couple meets the woman of the other.</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/095080-000-A/doch-das-boese-gibt-es-nicht/</t>
+          <t>https://www.3sat.de/film/spielfilm/hautnah-100.html</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/there-is-no-evil/</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/closer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="43" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Freier Atem</t>
+          <t>Doch das Böse gibt es nicht</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6898,44 +6898,44 @@
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Márta Mészáros</t>
+          <t>Mohammad Rasoulof</t>
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="F134" s="4" t="n"/>
       <c r="G134" s="5" t="n">
-        <v>289</v>
+        <v>15861</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>26.06.2026</t>
+          <t>19.02.2024</t>
         </is>
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>Jutka, a young woman who works in a factory, falls in love with Andras, a university student. She pretends to be a student, to him and to his parents, and begins to live a lie. Finally she rebels against Andras and his demands and the social conventions that forced her to live a lie.</t>
+          <t>Set against the backdrop of Iran's strict and oppressive legal system, this anthology film tells the stories of four men who each face a moral crisis when having to deal with death penalties.</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/132076-000-A/freier-atem/</t>
+          <t>https://www.arte.tv/de/videos/095080-000-A/doch-das-boese-gibt-es-nicht/</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/riddance/</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/there-is-no-evil/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="56" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Chefs Leckerbissen</t>
+          <t>Freier Atem</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6946,44 +6946,44 @@
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Nacho G. Velilla</t>
+          <t>Márta Mészáros</t>
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="F135" s="4" t="n"/>
       <c r="G135" s="5" t="n">
-        <v>1213</v>
+        <v>289</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>26.06.2026</t>
         </is>
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>Maxi thinks his life is perfect. He is a famous cook who owns a successful restaurant in Chueca and is living his life as a gay man without much complex. But when his son Edu and his daughter Alba appear, and a new attractive neighbor comes along, it will have a strong effect on his life resulting in his values being challenged for ever.</t>
+          <t>Jutka, a young woman who works in a factory, falls in love with Andras, a university student. She pretends to be a student, to him and to his parents, and begins to live a lie. Finally she rebels against Andras and his demands and the social conventions that forced her to live a lie.</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/130205-000-A/chefs-leckerbissen/</t>
+          <t>https://www.arte.tv/de/videos/132076-000-A/freier-atem/</t>
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/chefs-special/</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/riddance/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="69" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Die Nichtstuer</t>
+          <t>Chefs Leckerbissen</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6994,188 +6994,188 @@
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Nanni Moretti</t>
+          <t>Nacho G. Velilla</t>
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>3.69</v>
+        <v>3.02</v>
       </c>
       <c r="F136" s="4" t="n"/>
       <c r="G136" s="5" t="n">
-        <v>8874</v>
+        <v>1213</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>29.05.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="J136" s="6" t="inlineStr">
         <is>
-          <t>Four friends, former 1968 student protesters who have checked out of politics and struggle to come to terms with the present, try self-criticism to figure out what to do with themselves, only to end up doing what they do best: sinking into endless talk without ever reaching a conclusion.</t>
+          <t>Maxi thinks his life is perfect. He is a famous cook who owns a successful restaurant in Chueca and is living his life as a gay man without much complex. But when his son Edu and his daughter Alba appear, and a new attractive neighbor comes along, it will have a strong effect on his life resulting in his values being challenged for ever.</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/131534-000-A/die-nichtstuer/</t>
+          <t>https://www.arte.tv/de/videos/130205-000-A/chefs-leckerbissen/</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/ecce-bombo/</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/chefs-special/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="56" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Pleasure</t>
+          <t>Die Nichtstuer</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Ninja Thyberg</t>
+          <t>Nanni Moretti</t>
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>3.36</v>
+        <v>3.69</v>
       </c>
       <c r="F137" s="4" t="n"/>
       <c r="G137" s="5" t="n">
-        <v>91115</v>
+        <v>8874</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>28.07.2025</t>
+          <t>29.05.2026</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>19 year old Linnéa leaves her small town in Sweden and heads for Los Angeles with the aim of becoming the world's next big porn star, but the road to her goal turns out to be bumpier than she imagined.</t>
+          <t>Four friends, former 1968 student protesters who have checked out of politics and struggle to come to terms with the present, try self-criticism to figure out what to do with themselves, only to end up doing what they do best: sinking into endless talk without ever reaching a conclusion.</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/pleasure-100.html</t>
+          <t>https://www.arte.tv/de/videos/131534-000-A/die-nichtstuer/</t>
         </is>
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/pleasure-2021/</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/ecce-bombo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="43" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Margot und die Hochzeit</t>
+          <t>Pleasure</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Noah Baumbach</t>
+          <t>Ninja Thyberg</t>
         </is>
       </c>
       <c r="E138" s="3" t="n">
-        <v>3.23</v>
+        <v>3.36</v>
       </c>
       <c r="F138" s="4" t="n"/>
       <c r="G138" s="5" t="n">
-        <v>29576</v>
+        <v>91115</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>25.06.2026</t>
+          <t>28.07.2025</t>
         </is>
       </c>
       <c r="J138" s="6" t="inlineStr">
         <is>
-          <t>Margot Zeller is a short story writer with a sharp wit and an even sharper tongue. On the eve of her estranged sister Pauline's wedding to unemployed musician/artist/depressive Malcolm at the family seaside home, Margot shows up unexpectedly to rekindle the sisterly bond and offer her own brand of support. What ensues is a nakedly honest and subversively funny look at family dynamics.</t>
+          <t>19 year old Linnéa leaves her small town in Sweden and heads for Los Angeles with the aim of becoming the world's next big porn star, but the road to her goal turns out to be bumpier than she imagined.</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/132066-000-A/margot-und-die-hochzeit/</t>
+          <t>https://www.3sat.de/film/spielfilm/pleasure-100.html</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/margot-at-the-wedding/</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="82" customHeight="1">
+          <t>https://letterboxd.com/film/pleasure-2021/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="69" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Jussi Adler-Olsen: Verheißung</t>
+          <t>Margot und die Hochzeit</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>ZDF</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Ole Christian Madsen</t>
+          <t>Noah Baumbach</t>
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>2.81</v>
+        <v>3.23</v>
       </c>
       <c r="F139" s="4" t="n"/>
       <c r="G139" s="5" t="n">
-        <v>2504</v>
+        <v>29576</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>25.06.2026</t>
         </is>
       </c>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>In a moment of cowardice, Detective Carl Mørck sends Rose, his junior colleague in Department Q, to the remote Danish island of Bornholm to answer his old colleague Christian Habersaat's repeated requests. But during his forced retirement ceremony Christian kills himself sending Rose into a journey deep into her own traumatic past. Later, Department Q are embroiled into an old cold case of a girl found dead hanging in a tree.</t>
+          <t>Margot Zeller is a short story writer with a sharp wit and an even sharper tongue. On the eve of her estranged sister Pauline's wedding to unemployed musician/artist/depressive Malcolm at the family seaside home, Margot shows up unexpectedly to rekindle the sisterly bond and offer her own brand of support. What ensues is a nakedly honest and subversively funny look at family dynamics.</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/jussi-adler-olsen-verheissung-movie-100</t>
+          <t>https://www.arte.tv/de/videos/132066-000-A/margot-und-die-hochzeit/</t>
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/boundless-2024/</t>
+          <t>https://letterboxd.com/film/margot-at-the-wedding/</t>
         </is>
       </c>
     </row>
     <row r="140" ht="82" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Rosenthal</t>
+          <t>Jussi Adler-Olsen: Verheißung</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -7186,92 +7186,92 @@
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Oliver Haffner</t>
+          <t>Ole Christian Madsen</t>
         </is>
       </c>
       <c r="E140" s="3" t="n">
-        <v>3.35</v>
+        <v>2.81</v>
       </c>
       <c r="F140" s="4" t="n"/>
       <c r="G140" s="5" t="n">
-        <v>230</v>
+        <v>2504</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="J140" s="6" t="inlineStr">
         <is>
-          <t>Hans Rosenthal ist auf dem Höhepunkt seiner Karriere: als Liebling der Nation. Die 75. Ausgabe seines Straßenfegers "Dalli Dalli" steht kurz vor der Ausstrahlung. Doch die Feierlaune wird durch eine Entscheidung des Senders getrübt: Seine Jubiläumsshow fällt ausgerechnet auf den 9. November – 40 Jahre zuvor fanden rund um den 9. November die antisemitischen Pogrome statt. Rosenthal steckt in einem moralischen Dilemma.</t>
+          <t>In a moment of cowardice, Detective Carl Mørck sends Rose, his junior colleague in Department Q, to the remote Danish island of Bornholm to answer his old colleague Christian Habersaat's repeated requests. But during his forced retirement ceremony Christian kills himself sending Rose into a journey deep into her own traumatic past. Later, Department Q are embroiled into an old cold case of a girl found dead hanging in a tree.</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/rosenthal-movie-100</t>
+          <t>https://www.zdf.de/filme/jussi-adler-olsen-verheissung-movie-100</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/rosenthal/</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/boundless-2024/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="82" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Anatomie eines Mordes</t>
+          <t>Rosenthal</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ZDF</t>
         </is>
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Otto Preminger</t>
+          <t>Oliver Haffner</t>
         </is>
       </c>
       <c r="E141" s="3" t="n">
-        <v>4.24</v>
+        <v>3.35</v>
       </c>
       <c r="F141" s="4" t="n"/>
       <c r="G141" s="5" t="n">
-        <v>94095</v>
+        <v>230</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>154</v>
+        <v>92</v>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>21.09.2025</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>Semi-retired Michigan lawyer Paul Biegler takes the case of Army Lt. Manion, who murdered a local innkeeper after his wife claimed that he raped her. Over the course of an extensive trial, Biegler parries with District Attorney Lodwick and out-of-town prosecutor Claude Dancer to set his client free, but his case rests on the victim's mysterious business partner, who's hiding a dark secret.</t>
+          <t>Hans Rosenthal ist auf dem Höhepunkt seiner Karriere: als Liebling der Nation. Die 75. Ausgabe seines Straßenfegers "Dalli Dalli" steht kurz vor der Ausstrahlung. Doch die Feierlaune wird durch eine Entscheidung des Senders getrübt: Seine Jubiläumsshow fällt ausgerechnet auf den 9. November – 40 Jahre zuvor fanden rund um den 9. November die antisemitischen Pogrome statt. Rosenthal steckt in einem moralischen Dilemma.</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/anatomie-eines-mordes-106.html</t>
+          <t>https://www.zdf.de/filme/rosenthal-movie-100</t>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/anatomy-of-a-murder/</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/rosenthal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="69" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Bonjour Tristesse</t>
+          <t>Anatomie eines Mordes</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -7286,51 +7286,51 @@
         </is>
       </c>
       <c r="E142" s="3" t="n">
-        <v>3.64</v>
+        <v>4.24</v>
       </c>
       <c r="F142" s="4" t="n"/>
       <c r="G142" s="5" t="n">
-        <v>14676</v>
+        <v>94095</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>18.04.2025</t>
+          <t>21.09.2025</t>
         </is>
       </c>
       <c r="J142" s="6" t="inlineStr">
         <is>
-          <t>A spoiled teenager spends the summer at the French Riviera with her rich, widower, playboy father, but when his old flame resurfaces, she resolves to keep her frivolous lifestyle at all costs.</t>
+          <t>Semi-retired Michigan lawyer Paul Biegler takes the case of Army Lt. Manion, who murdered a local innkeeper after his wife claimed that he raped her. Over the course of an extensive trial, Biegler parries with District Attorney Lodwick and out-of-town prosecutor Claude Dancer to set his client free, but his case rests on the victim's mysterious business partner, who's hiding a dark secret.</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/bonjour-tristesse-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/anatomie-eines-mordes-106.html</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/bonjour-tristesse/</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="30" customHeight="1">
+          <t>https://letterboxd.com/film/anatomy-of-a-murder/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="43" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Bonjour Tristesse</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>ARD</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Pablo Larraín</t>
+          <t>Otto Preminger</t>
         </is>
       </c>
       <c r="E143" s="3" t="n">
@@ -7338,89 +7338,89 @@
       </c>
       <c r="F143" s="4" t="n"/>
       <c r="G143" s="5" t="n">
-        <v>417211</v>
+        <v>14676</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>30.05.2026</t>
+          <t>18.04.2025</t>
         </is>
       </c>
       <c r="J143" s="6" t="inlineStr">
         <is>
-          <t>During her Christmas holidays with the royal family at the Sandringham estate in Norfolk, England, Diana decides to leave her marriage to Prince Charles.</t>
+          <t>A spoiled teenager spends the summer at the French Riviera with her rich, widower, playboy father, but when his old flame resurfaces, she resolves to keep her frivolous lifestyle at all costs.</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS8xZjE4NTM4Yi0wOGMyLTQ3N2UtYTQyYS1kZDk5M2I1MmNiNmVfZ2FuemVTZW5kdW5n</t>
+          <t>https://www.3sat.de/film/spielfilm/bonjour-tristesse-100.html</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/spencer-2021/</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="108" customHeight="1">
+          <t>https://letterboxd.com/film/bonjour-tristesse/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="30" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Die Frau von gegenüber</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>ARD</t>
         </is>
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Patrice Leconte</t>
+          <t>Pablo Larraín</t>
         </is>
       </c>
       <c r="E144" s="3" t="n">
-        <v>3.06</v>
+        <v>3.64</v>
       </c>
       <c r="F144" s="4" t="n"/>
       <c r="G144" s="5" t="n">
-        <v>1457</v>
+        <v>417211</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>17.06.2026</t>
+          <t>30.05.2026</t>
         </is>
       </c>
       <c r="J144" s="6" t="inlineStr">
         <is>
-          <t>Abandoned by his wife, Bernard struggles to overcome his grief and settles in a residence for singles. Employed by "SOS Doctors", he provides night guards to occupy his insomnia. That's how he is brought one night to help a neighbor, Nadine Foulon, victim of discomfort in the elevator. It turns out that Nadine is also going through a difficult time, since her companion, Terry, a singer-guitarist, has left her. A professional photographer, she can not forget it and has since oscillated between depression and bulimia. Gathered by their pains of heart, these two beings will, with the wire of the confidences, become more intimate ...</t>
+          <t>During her Christmas holidays with the royal family at the Sandringham estate in Norfolk, England, Diana decides to leave her marriage to Prince Charles.</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/129308-000-A/die-frau-von-gegenueber/</t>
+          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS8xZjE4NTM4Yi0wOGMyLTQ3N2UtYTQyYS1kZDk5M2I1MmNiNmVfZ2FuemVTZW5kdW5n</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/singles-1982/</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/spencer-2021/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="108" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Maigret und das tote Mädchen</t>
+          <t>Die Frau von gegenüber</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C145" s="2" t="n"/>
@@ -7430,40 +7430,40 @@
         </is>
       </c>
       <c r="E145" s="3" t="n">
-        <v>2.76</v>
+        <v>3.06</v>
       </c>
       <c r="F145" s="4" t="n"/>
       <c r="G145" s="5" t="n">
-        <v>6313</v>
+        <v>1457</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>23.08.2025</t>
+          <t>17.06.2026</t>
         </is>
       </c>
       <c r="J145" s="6" t="inlineStr">
         <is>
-          <t>In Paris, a young girl is found dead in a Parisian square, wearing an evening dress. Commissioner Maigret will try to identify her and then understand what happened to the victim.</t>
+          <t>Abandoned by his wife, Bernard struggles to overcome his grief and settles in a residence for singles. Employed by "SOS Doctors", he provides night guards to occupy his insomnia. That's how he is brought one night to help a neighbor, Nadine Foulon, victim of discomfort in the elevator. It turns out that Nadine is also going through a difficult time, since her companion, Terry, a singer-guitarist, has left her. A professional photographer, she can not forget it and has since oscillated between depression and bulimia. Gathered by their pains of heart, these two beings will, with the wire of the confidences, become more intimate ...</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/maigret-und-das-tote-maedchen-100.html</t>
+          <t>https://www.arte.tv/de/videos/129308-000-A/die-frau-von-gegenueber/</t>
         </is>
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/maigret-2022/</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="82" customHeight="1">
+          <t>https://letterboxd.com/film/singles-1982/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="43" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>The Card Counter</t>
+          <t>Maigret und das tote Mädchen</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -7474,92 +7474,92 @@
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Paul Schrader</t>
+          <t>Patrice Leconte</t>
         </is>
       </c>
       <c r="E146" s="3" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="F146" s="4" t="n"/>
       <c r="G146" s="5" t="n">
-        <v>132077</v>
+        <v>6313</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>07.11.2025</t>
+          <t>23.08.2025</t>
         </is>
       </c>
       <c r="J146" s="6" t="inlineStr">
         <is>
-          <t>William Tell just wants to play cards. His spartan existence on the casino trail is shattered when he is approached by Cirk, a vulnerable and angry young man seeking help to execute his plan for revenge on a military colonel. Tell sees a chance at redemption through his relationship with Cirk. But keeping Cirk on the straight-and-narrow proves impossible, dragging Tell back into the darkness of his past.</t>
+          <t>In Paris, a young girl is found dead in a Parisian square, wearing an evening dress. Commissioner Maigret will try to identify her and then understand what happened to the victim.</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/the-card-counter-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/maigret-und-das-tote-maedchen-100.html</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-card-counter/</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="30" customHeight="1">
+          <t>https://letterboxd.com/film/maigret-2022/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="82" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Last Exit Reno</t>
+          <t>The Card Counter</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Paul Thomas Anderson</t>
+          <t>Paul Schrader</t>
         </is>
       </c>
       <c r="E147" s="3" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="F147" s="4" t="n"/>
       <c r="G147" s="5" t="n">
-        <v>140124</v>
+        <v>132077</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>17.03.2026</t>
+          <t>07.11.2025</t>
         </is>
       </c>
       <c r="J147" s="6" t="inlineStr">
         <is>
-          <t>A stranger mentors a young Reno gambler who weds a hooker and befriends a vulgar casino regular.</t>
+          <t>William Tell just wants to play cards. His spartan existence on the casino trail is shattered when he is approached by Cirk, a vulnerable and angry young man seeking help to execute his plan for revenge on a military colonel. Tell sees a chance at redemption through his relationship with Cirk. But keeping Cirk on the straight-and-narrow proves impossible, dragging Tell back into the darkness of his past.</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/130328-000-A/last-exit-reno/</t>
+          <t>https://www.3sat.de/film/spielfilm/the-card-counter-100.html</t>
         </is>
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/hard-eight/</t>
+          <t>https://letterboxd.com/film/the-card-counter/</t>
         </is>
       </c>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Frauen am Rande des Nervenzusammenbruchs</t>
+          <t>Last Exit Reno</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7570,46 +7570,44 @@
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Pedro Almodóvar</t>
+          <t>Paul Thomas Anderson</t>
         </is>
       </c>
       <c r="E148" s="3" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="F148" s="4" t="n">
-        <v>4</v>
-      </c>
+        <v>3.62</v>
+      </c>
+      <c r="F148" s="4" t="n"/>
       <c r="G148" s="5" t="n">
-        <v>237339</v>
+        <v>140124</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>06.05.2019</t>
+          <t>17.03.2026</t>
         </is>
       </c>
       <c r="J148" s="6" t="inlineStr">
         <is>
-          <t>After being dumped by her lover, Pepa finds her life and the lives of those around her spiraling out of control in a deliciously chaotic series of events.</t>
+          <t>A stranger mentors a young Reno gambler who weds a hooker and befriends a vulgar casino regular.</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/036694-000-A/frauen-am-rande-des-nervenzusammenbruchs/</t>
+          <t>https://www.arte.tv/de/videos/130328-000-A/last-exit-reno/</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/women-on-the-verge-of-a-nervous-breakdown/</t>
+          <t>https://letterboxd.com/film/hard-eight/</t>
         </is>
       </c>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Volver - Zurückkehren</t>
+          <t>Frauen am Rande des Nervenzusammenbruchs</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7624,40 +7622,42 @@
         </is>
       </c>
       <c r="E149" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F149" s="4" t="n"/>
+        <v>4.12</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="G149" s="5" t="n">
-        <v>205279</v>
+        <v>237339</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>06.05.2019</t>
         </is>
       </c>
       <c r="J149" s="6" t="inlineStr">
         <is>
-          <t>Three generations of women deal with family secrets while surviving the east wind, fire, insanity, superstition, lies and even death.</t>
+          <t>After being dumped by her lover, Pepa finds her life and the lives of those around her spiraling out of control in a deliciously chaotic series of events.</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/043486-000-A/volver-zurueckkehren/</t>
+          <t>https://www.arte.tv/de/videos/036694-000-A/frauen-am-rande-des-nervenzusammenbruchs/</t>
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/volver/</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="82" customHeight="1">
+          <t>https://letterboxd.com/film/women-on-the-verge-of-a-nervous-breakdown/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="30" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Leid und Herrlichkeit</t>
+          <t>Volver - Zurückkehren</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -7672,42 +7672,40 @@
         </is>
       </c>
       <c r="E150" s="3" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="F150" s="4" t="n">
-        <v>5</v>
-      </c>
+        <v>4.1</v>
+      </c>
+      <c r="F150" s="4" t="n"/>
       <c r="G150" s="5" t="n">
-        <v>169519</v>
+        <v>205279</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>08.05.2022</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="J150" s="6" t="inlineStr">
         <is>
-          <t>Salvador Mallo, a filmmaker in the twilight of his career, remembers his life: his mother, his lovers, the actors he worked with. The sixties in a small village in Valencia, the eighties in Madrid, the present, when he feels an immeasurable emptiness, facing his mortality, the incapability of continuing filming, the impossibility of separating creation from his own life. The need of narrating his past can be his salvation.</t>
+          <t>Three generations of women deal with family secrets while surviving the east wind, fire, insanity, superstition, lies and even death.</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/094468-000-A/leid-und-herrlichkeit/</t>
+          <t>https://www.arte.tv/de/videos/043486-000-A/volver-zurueckkehren/</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/pain-and-glory/</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/volver/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="82" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>La Mala Educación - Schlechte Erziehung</t>
+          <t>Leid und Herrlichkeit</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -7722,42 +7720,42 @@
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="F151" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>120485</v>
+        <v>169519</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>08.05.2019</t>
+          <t>08.05.2022</t>
         </is>
       </c>
       <c r="J151" s="6" t="inlineStr">
         <is>
-          <t>When an old friend brings filmmaker Enrique Goded a semi-autobiographical script chronicling their adolescence, Enrique is forced to relive his youth spent at a Catholic boarding school.</t>
+          <t>Salvador Mallo, a filmmaker in the twilight of his career, remembers his life: his mother, his lovers, the actors he worked with. The sixties in a small village in Valencia, the eighties in Madrid, the present, when he feels an immeasurable emptiness, facing his mortality, the incapability of continuing filming, the impossibility of separating creation from his own life. The need of narrating his past can be his salvation.</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/040192-000-A/la-mala-educacion-schlechte-erziehung/</t>
+          <t>https://www.arte.tv/de/videos/094468-000-A/leid-und-herrlichkeit/</t>
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/bad-education/</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="30" customHeight="1">
+          <t>https://letterboxd.com/film/pain-and-glory/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="43" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Sprich mit ihr</t>
+          <t>La Mala Educación - Schlechte Erziehung</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -7772,42 +7770,42 @@
         </is>
       </c>
       <c r="E152" s="3" t="n">
-        <v>3.87</v>
+        <v>3.96</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>105398</v>
+        <v>120485</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>06.05.2019</t>
+          <t>08.05.2019</t>
         </is>
       </c>
       <c r="J152" s="6" t="inlineStr">
         <is>
-          <t>Two men share an odd friendship while they care for two women who are both in deep comas.</t>
+          <t>When an old friend brings filmmaker Enrique Goded a semi-autobiographical script chronicling their adolescence, Enrique is forced to relive his youth spent at a Catholic boarding school.</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/039137-000-A/sprich-mit-ihr/</t>
+          <t>https://www.arte.tv/de/videos/040192-000-A/la-mala-educacion-schlechte-erziehung/</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/talk-to-her/</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="82" customHeight="1">
+          <t>https://letterboxd.com/film/bad-education/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="30" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Live Flesh - Mit Haut und Haar</t>
+          <t>Sprich mit ihr</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -7822,184 +7820,186 @@
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F153" s="4" t="n"/>
+        <v>3.87</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="G153" s="5" t="n">
-        <v>47554</v>
+        <v>105398</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>01.05.2026</t>
+          <t>06.05.2019</t>
         </is>
       </c>
       <c r="J153" s="6" t="inlineStr">
         <is>
-          <t>When Victor attempts to seduce Elena, all he gets for his trouble is a one-way, six-year ticket to prison, where he concentrates on strengthening his mind, his body... and his desire for vengeance on the man who put him there. After his release and still madly in love with her, Victor will stop at nothing to win her over even if means revenge, for Elena has married David, the cop who sent him to prison!</t>
+          <t>Two men share an odd friendship while they care for two women who are both in deep comas.</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/030301-000-A/live-flesh-mit-haut-und-haar/</t>
+          <t>https://www.arte.tv/de/videos/039137-000-A/sprich-mit-ihr/</t>
         </is>
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/live-flesh/</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/talk-to-her/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="82" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Vanished - Tage der Angst</t>
+          <t>Live Flesh - Mit Haut und Haar</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>ZDF</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C154" s="2" t="n"/>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Peter Facinelli</t>
+          <t>Pedro Almodóvar</t>
         </is>
       </c>
       <c r="E154" s="3" t="n">
-        <v>2.49</v>
+        <v>3.7</v>
       </c>
       <c r="F154" s="4" t="n"/>
       <c r="G154" s="5" t="n">
-        <v>10203</v>
+        <v>47554</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>08.06.2026</t>
+          <t>01.05.2026</t>
         </is>
       </c>
       <c r="J154" s="6" t="inlineStr">
         <is>
-          <t>A family vacation takes a terrifying turn when parents Paul and Wendy discover their young daughter has vanished without a trace. Stopping at nothing to find her, the search for the truth leads to a shocking revelation.</t>
+          <t>When Victor attempts to seduce Elena, all he gets for his trouble is a one-way, six-year ticket to prison, where he concentrates on strengthening his mind, his body... and his desire for vengeance on the man who put him there. After his release and still madly in love with her, Victor will stop at nothing to win her over even if means revenge, for Elena has married David, the cop who sent him to prison!</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/vanished---tage-der-angst-movie-100</t>
+          <t>https://www.arte.tv/de/videos/030301-000-A/live-flesh-mit-haut-und-haar/</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-vanished-2020/</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="17" customHeight="1">
+          <t>https://letterboxd.com/film/live-flesh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="43" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Schweinehaut</t>
+          <t>Vanished - Tage der Angst</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>ZDF</t>
         </is>
       </c>
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Philippe Katerine</t>
+          <t>Peter Facinelli</t>
         </is>
       </c>
       <c r="E155" s="3" t="n">
-        <v>3.42</v>
+        <v>2.49</v>
       </c>
       <c r="F155" s="4" t="n"/>
       <c r="G155" s="5" t="n">
-        <v>216</v>
+        <v>10203</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>28.04.2026</t>
+          <t>08.06.2026</t>
         </is>
       </c>
       <c r="J155" s="6" t="inlineStr">
         <is>
-          <t>Twelve sequences in the life of singer/musician Philippe Katerine.</t>
+          <t>A family vacation takes a terrifying turn when parents Paul and Wendy discover their young daughter has vanished without a trace. Stopping at nothing to find her, the search for the truth leads to a shocking revelation.</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/131539-000-A/schweinehaut/</t>
+          <t>https://www.zdf.de/filme/vanished---tage-der-angst-movie-100</t>
         </is>
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/pigskin-2005/</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="82" customHeight="1">
+          <t>https://letterboxd.com/film/the-vanished-2020/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="17" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Alibi.com 2</t>
+          <t>Schweinehaut</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>ZDF</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C156" s="2" t="n"/>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Philippe Lacheau</t>
+          <t>Philippe Katerine</t>
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>2.78</v>
+        <v>3.42</v>
       </c>
       <c r="F156" s="4" t="n"/>
       <c r="G156" s="5" t="n">
-        <v>29602</v>
+        <v>216</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>26.06.2026</t>
+          <t>28.04.2026</t>
         </is>
       </c>
       <c r="J156" s="6" t="inlineStr">
         <is>
-          <t>After closing his agency Alibi.com and promising Flo that he would never lie to her again, Greg's new life became quiet, too quiet... Not for long! When he decides to propose to Flo, Greg is up against the wall and has to introduce his family. But with his crooked father and his ex-charm actress mother, this could ruin his future union. He has no choice but to reopen his agency with his former accomplices for an ultimate Alibi and to find more presentable fake parents.</t>
+          <t>Twelve sequences in the life of singer/musician Philippe Katerine.</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/alibicom-2-movie-100</t>
+          <t>https://www.arte.tv/de/videos/131539-000-A/schweinehaut/</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/alibicom-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/pigskin-2005/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="82" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Canary Black</t>
+          <t>Alibi.com 2</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -8010,44 +8010,44 @@
       <c r="C157" s="2" t="n"/>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Pierre Morel</t>
+          <t>Philippe Lacheau</t>
         </is>
       </c>
       <c r="E157" s="3" t="n">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="F157" s="4" t="n"/>
       <c r="G157" s="5" t="n">
-        <v>8584</v>
+        <v>29602</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>11.06.2026</t>
+          <t>26.06.2026</t>
         </is>
       </c>
       <c r="J157" s="6" t="inlineStr">
         <is>
-          <t>Top level CIA agent Avery Graves is blackmailed by terrorists into betraying her own country to save her kidnapped husband. Cut off from her team, she turns to her underworld contacts to survive and help locate the coveted intelligence that the kidnappers want.</t>
+          <t>After closing his agency Alibi.com and promising Flo that he would never lie to her again, Greg's new life became quiet, too quiet... Not for long! When he decides to propose to Flo, Greg is up against the wall and has to introduce his family. But with his crooked father and his ex-charm actress mother, this could ruin his future union. He has no choice but to reopen his agency with his former accomplices for an ultimate Alibi and to find more presentable fake parents.</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/canary-black-movie-100</t>
+          <t>https://www.zdf.de/filme/alibicom-2-movie-100</t>
         </is>
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/canary-black/</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/alibicom-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="56" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Greedy People - Gelegenheit macht gierig</t>
+          <t>Canary Black</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -8058,44 +8058,44 @@
       <c r="C158" s="2" t="n"/>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Potsy Ponciroli</t>
+          <t>Pierre Morel</t>
         </is>
       </c>
       <c r="E158" s="3" t="n">
-        <v>3.06</v>
+        <v>2.28</v>
       </c>
       <c r="F158" s="4" t="n"/>
       <c r="G158" s="5" t="n">
-        <v>21207</v>
+        <v>8584</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>23.06.2026</t>
+          <t>11.06.2026</t>
         </is>
       </c>
       <c r="J158" s="6" t="inlineStr">
         <is>
-          <t>The eclectic residents of a small, picturesque island town must navigate a sensational murder and the discovery of a million dollars, leading to a series of increasingly bad decisions which upend the once-peaceful community.</t>
+          <t>Top level CIA agent Avery Graves is blackmailed by terrorists into betraying her own country to save her kidnapped husband. Cut off from her team, she turns to her underworld contacts to survive and help locate the coveted intelligence that the kidnappers want.</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/greedy-people---gelegenheit-macht-gierig-movie-100</t>
+          <t>https://www.zdf.de/filme/canary-black-movie-100</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/greedy-people/</t>
+          <t>https://letterboxd.com/film/canary-black/</t>
         </is>
       </c>
     </row>
     <row r="159" ht="43" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>See for Me - Der unsichtbare Feind</t>
+          <t>Greedy People - Gelegenheit macht gierig</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -8106,241 +8106,241 @@
       <c r="C159" s="2" t="n"/>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Randall Okita</t>
+          <t>Potsy Ponciroli</t>
         </is>
       </c>
       <c r="E159" s="3" t="n">
-        <v>2.75</v>
+        <v>3.06</v>
       </c>
       <c r="F159" s="4" t="n"/>
       <c r="G159" s="5" t="n">
-        <v>17103</v>
+        <v>21207</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>28.05.2026</t>
+          <t>23.06.2026</t>
         </is>
       </c>
       <c r="J159" s="6" t="inlineStr">
         <is>
-          <t>When blind former Olympic skier Sophie Scott cat-sits in a secluded mansion, she gets caught in the crossfire of a home invasion scheme. She must rely on a sighted Army veteran via the See for Me app to help her survive the night.</t>
+          <t>The eclectic residents of a small, picturesque island town must navigate a sensational murder and the discovery of a million dollars, leading to a series of increasingly bad decisions which upend the once-peaceful community.</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/see-for-me---der-unsichtbare-feind-movie-100</t>
+          <t>https://www.zdf.de/filme/greedy-people---gelegenheit-macht-gierig-movie-100</t>
         </is>
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/see-for-me/</t>
+          <t>https://letterboxd.com/film/greedy-people/</t>
         </is>
       </c>
     </row>
     <row r="160" ht="43" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Die Geheimnisse von Lissabon</t>
+          <t>See for Me - Der unsichtbare Feind</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>ZDF</t>
         </is>
       </c>
       <c r="C160" s="2" t="n"/>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Raúl Ruiz</t>
+          <t>Randall Okita</t>
         </is>
       </c>
       <c r="E160" s="3" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="F160" s="4" t="n"/>
       <c r="G160" s="5" t="n">
-        <v>4259</v>
+        <v>17103</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>249</v>
+        <v>84</v>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>21.05.2026</t>
+          <t>28.05.2026</t>
         </is>
       </c>
       <c r="J160" s="6" t="inlineStr">
         <is>
-          <t>The tragic story of the many lives of Father Dinis, his dark origins and his pious works, and the different fates of all those who, trapped in a sinister web of love, hate and crime, cross paths with him through years of adventure.</t>
+          <t>When blind former Olympic skier Sophie Scott cat-sits in a secluded mansion, she gets caught in the crossfire of a home invasion scheme. She must rely on a sighted Army veteran via the See for Me app to help her survive the night.</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/131183-000-A/die-geheimnisse-von-lissabon/</t>
+          <t>https://www.zdf.de/filme/see-for-me---der-unsichtbare-feind-movie-100</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/mysteries-of-lisbon-2010/</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="30" customHeight="1">
+          <t>https://letterboxd.com/film/see-for-me/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="43" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>22 Kugeln – Die Rache des Profis</t>
+          <t>Die Geheimnisse von Lissabon</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C161" s="2" t="n"/>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Richard Berry</t>
+          <t>Raúl Ruiz</t>
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>3.11</v>
+        <v>4.1</v>
       </c>
       <c r="F161" s="4" t="n"/>
       <c r="G161" s="5" t="n">
-        <v>11363</v>
+        <v>4259</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>104</v>
+        <v>249</v>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>05.12.2025</t>
+          <t>21.05.2026</t>
         </is>
       </c>
       <c r="J161" s="6" t="inlineStr">
         <is>
-          <t>A retired mobster goes on a revenge spree after being left for dead with 22 bullets in his body by his former childhood friend.</t>
+          <t>The tragic story of the many lives of Father Dinis, his dark origins and his pious works, and the different fates of all those who, trapped in a sinister web of love, hate and crime, cross paths with him through years of adventure.</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/22-kugeln-die-rache-des-profis-106.html</t>
+          <t>https://www.arte.tv/de/videos/131183-000-A/die-geheimnisse-von-lissabon/</t>
         </is>
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/22-bullets/</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="82" customHeight="1">
+          <t>https://letterboxd.com/film/mysteries-of-lisbon-2010/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="30" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Adel verpflichtet</t>
+          <t>22 Kugeln – Die Rache des Profis</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C162" s="2" t="n"/>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Robert Hamer</t>
+          <t>Richard Berry</t>
         </is>
       </c>
       <c r="E162" s="3" t="n">
-        <v>4.07</v>
+        <v>3.11</v>
       </c>
       <c r="F162" s="4" t="n"/>
       <c r="G162" s="5" t="n">
-        <v>28551</v>
+        <v>11363</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>14.06.2026</t>
+          <t>05.12.2025</t>
         </is>
       </c>
       <c r="J162" s="6" t="inlineStr">
         <is>
-          <t>When his mother eloped with an Italian opera singer, Louis Mazzini was cut off from her aristocratic family. After the family refuses to let her be buried in the family mausoleum, Louis avenges his mother's death by attempting to murder every family member who stands between himself and the family fortune. But when he finds himself torn between his longtime love and the widow of one of his victims, his plans go awry.</t>
+          <t>A retired mobster goes on a revenge spree after being left for dead with 22 bullets in his body by his former childhood friend.</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/040683-000-A/adel-verpflichtet/</t>
+          <t>https://www.3sat.de/film/spielfilm/22-kugeln-die-rache-des-profis-106.html</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/kind-hearts-and-coronets/</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/22-bullets/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="82" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Der Schut</t>
+          <t>Adel verpflichtet</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>ARD</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C163" s="2" t="n"/>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Robert Siodmak</t>
+          <t>Robert Hamer</t>
         </is>
       </c>
       <c r="E163" s="3" t="n">
-        <v>3.17</v>
+        <v>4.07</v>
       </c>
       <c r="F163" s="4" t="n"/>
       <c r="G163" s="5" t="n">
-        <v>479</v>
+        <v>28551</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>25.05.2026</t>
+          <t>14.06.2026</t>
         </is>
       </c>
       <c r="J163" s="6" t="inlineStr">
         <is>
-          <t>When a villain named "Der Schut" terrorizes the constituents of Albanian country, which he rules, heroic Kara Ben Nemsi and his sidekick are the only ones who can stop him.</t>
+          <t>When his mother eloped with an Italian opera singer, Louis Mazzini was cut off from her aristocratic family. After the family refuses to let her be buried in the family mausoleum, Louis avenges his mother's death by attempting to murder every family member who stands between himself and the family fortune. But when he finds himself torn between his longtime love and the widow of one of his victims, his plans go awry.</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS9lZDBmZTIyYi1hZmVjLTQzMTctYmFmNi1kYzdhN2JmZTkzNDFfZ2FuemVTZW5kdW5n</t>
+          <t>https://www.arte.tv/de/videos/040683-000-A/adel-verpflichtet/</t>
         </is>
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/yellow-devil/</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/kind-hearts-and-coronets/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="43" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Die Pyramide des Sonnengottes</t>
+          <t>Der Schut</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARD</t>
         </is>
       </c>
       <c r="C164" s="2" t="n"/>
@@ -8350,376 +8350,376 @@
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="F164" s="4" t="n"/>
       <c r="G164" s="5" t="n">
-        <v>299</v>
+        <v>479</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>24.05.2026</t>
+          <t>25.05.2026</t>
         </is>
       </c>
       <c r="J164" s="6" t="inlineStr">
         <is>
-          <t>Mexico, 1864. The country is divided by the struggle against the French occupation and emperor Maximilian. The German doctor Karl Sternau and his friend Andreas Hasenpfeffer come to love the country and support the cause of the proud Mexicans.</t>
+          <t>When a villain named "Der Schut" terrorizes the constituents of Albanian country, which he rules, heroic Kara Ben Nemsi and his sidekick are the only ones who can stop him.</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/die-pyramide-des-sonnengottes-100.html</t>
+          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS9lZDBmZTIyYi1hZmVjLTQzMTctYmFmNi1kYzdhN2JmZTkzNDFfZ2FuemVTZW5kdW5n</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/pyramid-of-the-sun-god/</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/yellow-devil/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="56" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Wie wilde Tiere</t>
+          <t>Die Pyramide des Sonnengottes</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C165" s="2" t="n"/>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Sorogoyen</t>
+          <t>Robert Siodmak</t>
         </is>
       </c>
       <c r="E165" s="3" t="n">
-        <v>4.08</v>
+        <v>3.09</v>
       </c>
       <c r="F165" s="4" t="n"/>
       <c r="G165" s="5" t="n">
-        <v>100421</v>
+        <v>299</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>03.06.2026</t>
+          <t>24.05.2026</t>
         </is>
       </c>
       <c r="J165" s="6" t="inlineStr">
         <is>
-          <t>Antoine and Olga, a French couple, have been living in a small village in Galicia for a long time. They practice eco-responsible agriculture and restore abandoned houses to facilitate repopulation. Everything should be idyllic except for their opposition to a wind turbine project that creates a serious conflict with their neighbors. The tension will rise to the point of irreparability.</t>
+          <t>Mexico, 1864. The country is divided by the struggle against the French occupation and emperor Maximilian. The German doctor Karl Sternau and his friend Andreas Hasenpfeffer come to love the country and support the cause of the proud Mexicans.</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/120378-000-A/wie-wilde-tiere/</t>
+          <t>https://www.3sat.de/film/spielfilm/die-pyramide-des-sonnengottes-100.html</t>
         </is>
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-beasts-2022/</t>
+          <t>https://letterboxd.com/film/pyramid-of-the-sun-god/</t>
         </is>
       </c>
     </row>
     <row r="166" ht="69" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Geheimsache Malta</t>
+          <t>Wie wilde Tiere</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>ZDF</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C166" s="2" t="n"/>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Roel Reiné</t>
+          <t>Rodrigo Sorogoyen</t>
         </is>
       </c>
       <c r="E166" s="3" t="n">
-        <v>1.76</v>
+        <v>4.08</v>
       </c>
       <c r="F166" s="4" t="n"/>
       <c r="G166" s="5" t="n">
-        <v>1968</v>
+        <v>100421</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>03.06.2026</t>
         </is>
       </c>
       <c r="J166" s="6" t="inlineStr">
         <is>
-          <t>Operating alone in the field for more than 20 years, a CIA hitman uses the "Help Wanted" section of the newspapers to get his orders from the Agency. His long-lost daughter, now a UK MI6 analyst, tracks him down to deliver shocking news: his CIA boss has been dead for years and the division long since shut down. Together, they set out to discover whose orders he's been executing.</t>
+          <t>Antoine and Olga, a French couple, have been living in a small village in Galicia for a long time. They practice eco-responsible agriculture and restore abandoned houses to facilitate repopulation. Everything should be idyllic except for their opposition to a wind turbine project that creates a serious conflict with their neighbors. The tension will rise to the point of irreparability.</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/geheimsache-malta-movie-100</t>
+          <t>https://www.arte.tv/de/videos/120378-000-A/wie-wilde-tiere/</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/classified-2024/</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/the-beasts-2022/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="69" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Thirteen Days</t>
+          <t>Geheimsache Malta</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ZDF</t>
         </is>
       </c>
       <c r="C167" s="2" t="n"/>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Roger Donaldson</t>
+          <t>Roel Reiné</t>
         </is>
       </c>
       <c r="E167" s="3" t="n">
-        <v>3.39</v>
+        <v>1.76</v>
       </c>
       <c r="F167" s="4" t="n"/>
       <c r="G167" s="5" t="n">
-        <v>28244</v>
+        <v>1968</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>04.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="J167" s="6" t="inlineStr">
         <is>
-          <t>The story of the Cuban Missile Crisis in 1962—the nuclear standoff with the USSR sparked by the discovery by the Americans of missile bases established on the Soviet-allied island of Cuba.</t>
+          <t>Operating alone in the field for more than 20 years, a CIA hitman uses the "Help Wanted" section of the newspapers to get his orders from the Agency. His long-lost daughter, now a UK MI6 analyst, tracks him down to deliver shocking news: his CIA boss has been dead for years and the division long since shut down. Together, they set out to discover whose orders he's been executing.</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/thirteen-days-102.html</t>
+          <t>https://www.zdf.de/filme/geheimsache-malta-movie-100</t>
         </is>
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/thirteen-days/</t>
+          <t>https://letterboxd.com/film/classified-2024/</t>
         </is>
       </c>
     </row>
     <row r="168" ht="43" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Nackt</t>
+          <t>Thirteen Days</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C168" s="2" t="n"/>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Ruggero Deodato</t>
+          <t>Roger Donaldson</t>
         </is>
       </c>
       <c r="E168" s="3" t="n">
-        <v>2.61</v>
+        <v>3.39</v>
       </c>
       <c r="F168" s="4" t="n"/>
       <c r="G168" s="5" t="n">
-        <v>115579</v>
+        <v>28244</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>04.07.2026</t>
         </is>
       </c>
       <c r="J168" s="6" t="inlineStr">
         <is>
-          <t>A New York University professor returns from a rescue mission to the Amazon rainforest with the footage shot by a lost team of documentarians who were making a film about the area's local cannibal tribes.</t>
+          <t>The story of the Cuban Missile Crisis in 1962—the nuclear standoff with the USSR sparked by the discovery by the Americans of missile bases established on the Soviet-allied island of Cuba.</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/018434-000-A/nackt/</t>
+          <t>https://www.3sat.de/film/spielfilm/thirteen-days-102.html</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/cannibal-holocaust/</t>
+          <t>https://letterboxd.com/film/thirteen-days/</t>
         </is>
       </c>
     </row>
     <row r="169" ht="43" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Highlander: Es kann nur einen geben</t>
+          <t>Nackt</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C169" s="2" t="n"/>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Russell Mulcahy</t>
+          <t>Ruggero Deodato</t>
         </is>
       </c>
       <c r="E169" s="3" t="n">
-        <v>3.32</v>
+        <v>2.61</v>
       </c>
       <c r="F169" s="4" t="n"/>
       <c r="G169" s="5" t="n">
-        <v>112126</v>
+        <v>115579</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>28.02.2025</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="J169" s="6" t="inlineStr">
         <is>
-          <t>He fought his first battle on the Scottish Highlands in 1536. He will fight his greatest battle on the streets of New York City in 1986. His name is Connor MacLeod. He is immortal.</t>
+          <t>A New York University professor returns from a rescue mission to the Amazon rainforest with the footage shot by a lost team of documentarians who were making a film about the area's local cannibal tribes.</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/highlander-es-kann-nur-einen-geben-100.html</t>
+          <t>https://www.arte.tv/de/videos/018434-000-A/nackt/</t>
         </is>
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/highlander/</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/cannibal-holocaust/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="43" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Santosh</t>
+          <t>Highlander: Es kann nur einen geben</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C170" s="2" t="n"/>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Sandhya Suri</t>
+          <t>Russell Mulcahy</t>
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>3.61</v>
+        <v>3.32</v>
       </c>
       <c r="F170" s="4" t="n"/>
       <c r="G170" s="5" t="n">
-        <v>15092</v>
+        <v>112126</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>27.05.2026</t>
+          <t>28.02.2025</t>
         </is>
       </c>
       <c r="J170" s="6" t="inlineStr">
         <is>
-          <t>A government scheme sees newly widowed Santosh inherit her husband’s job as a police constable in the rural badlands of Northern India. When a low-caste girl is found raped and murdered, she is pulled into the investigation under the wing of charismatic feminist inspector Sharma.</t>
+          <t>He fought his first battle on the Scottish Highlands in 1536. He will fight his greatest battle on the streets of New York City in 1986. His name is Connor MacLeod. He is immortal.</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/098023-000-A/santosh/</t>
+          <t>https://www.3sat.de/film/spielfilm/highlander-es-kann-nur-einen-geben-100.html</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/santosh-2024/</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="160" customHeight="1">
+          <t>https://letterboxd.com/film/highlander/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="56" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Schweigend steht der Wald</t>
+          <t>Santosh</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C171" s="2" t="n"/>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Saralisa Volm</t>
+          <t>Sandhya Suri</t>
         </is>
       </c>
       <c r="E171" s="3" t="n">
-        <v>3.01</v>
+        <v>3.61</v>
       </c>
       <c r="F171" s="4" t="n"/>
       <c r="G171" s="5" t="n">
-        <v>739</v>
+        <v>15092</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>23.01.2026</t>
+          <t>27.05.2026</t>
         </is>
       </c>
       <c r="J171" s="6" t="inlineStr">
         <is>
-          <t>As a forestry student doing an internship, Anja Grimm ends up in that remote area in the Upper Palatinate Forest, where she went on vacation with her parents as an eight-year-old girl and her father disappeared without a trace. Her job is to take soil samples to create a soil map. At one point in the forest floor she comes across abnormal irregularities. Not long after their arrival, a brutal murder occurs. Anja soon arouses suspicion and hostility not only among the villagers with her suspicion that the perpetrator knows something about her father's fate and with her questions about the atypical soil composition in the forest clearing. Even the police react extremely reservedly to their investigations. And when it turns out that the young woman can read the signs of the forest like an open book, forces mobilize in the village who are apparently ready for anything because there is a dark secret that needs to be kept.</t>
+          <t>A government scheme sees newly widowed Santosh inherit her husband’s job as a police constable in the rural badlands of Northern India. When a low-caste girl is found raped and murdered, she is pulled into the investigation under the wing of charismatic feminist inspector Sharma.</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/schweigend-steht-der-wald-102.html</t>
+          <t>https://www.arte.tv/de/videos/098023-000-A/santosh/</t>
         </is>
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-silent-forest-2022/</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/santosh-2024/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="160" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>The Florida Project</t>
+          <t>Schweigend steht der Wald</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -8730,140 +8730,140 @@
       <c r="C172" s="2" t="n"/>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Sean Baker</t>
+          <t>Saralisa Volm</t>
         </is>
       </c>
       <c r="E172" s="3" t="n">
-        <v>4.1</v>
+        <v>3.01</v>
       </c>
       <c r="F172" s="4" t="n"/>
       <c r="G172" s="5" t="n">
-        <v>1065771</v>
+        <v>739</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>20.08.2025</t>
+          <t>23.01.2026</t>
         </is>
       </c>
       <c r="J172" s="6" t="inlineStr">
         <is>
-          <t>The story of a precocious six year-old and her ragtag group of friends whose summer break is filled with childhood wonder, possibility and a sense of adventure while the adults around them struggle with hard times.</t>
+          <t>As a forestry student doing an internship, Anja Grimm ends up in that remote area in the Upper Palatinate Forest, where she went on vacation with her parents as an eight-year-old girl and her father disappeared without a trace. Her job is to take soil samples to create a soil map. At one point in the forest floor she comes across abnormal irregularities. Not long after their arrival, a brutal murder occurs. Anja soon arouses suspicion and hostility not only among the villagers with her suspicion that the perpetrator knows something about her father's fate and with her questions about the atypical soil composition in the forest clearing. Even the police react extremely reservedly to their investigations. And when it turns out that the young woman can read the signs of the forest like an open book, forces mobilize in the village who are apparently ready for anything because there is a dark secret that needs to be kept.</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/the-florida-project-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/schweigend-steht-der-wald-102.html</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-florida-project/</t>
+          <t>https://letterboxd.com/film/the-silent-forest-2022/</t>
         </is>
       </c>
     </row>
     <row r="173" ht="43" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Es war einmal in Amerika</t>
+          <t>The Florida Project</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C173" s="2" t="n"/>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Sergio Leone</t>
+          <t>Sean Baker</t>
         </is>
       </c>
       <c r="E173" s="3" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="F173" s="4" t="n"/>
       <c r="G173" s="5" t="n">
-        <v>314152</v>
+        <v>1065771</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>217</v>
+        <v>107</v>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>08.06.2026</t>
+          <t>20.08.2025</t>
         </is>
       </c>
       <c r="J173" s="6" t="inlineStr">
         <is>
-          <t>A former Prohibition-era Jewish gangster returns to the Lower East Side of Manhattan over thirty years later, where he once again must confront the ghosts and regrets of his old life.</t>
+          <t>The story of a precocious six year-old and her ragtag group of friends whose summer break is filled with childhood wonder, possibility and a sense of adventure while the adults around them struggle with hard times.</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/046617-000-A/es-war-einmal-in-amerika/</t>
+          <t>https://www.3sat.de/film/spielfilm/the-florida-project-100.html</t>
         </is>
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/once-upon-a-time-in-america/</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="30" customHeight="1">
+          <t>https://letterboxd.com/film/the-florida-project/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="43" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Serpico</t>
+          <t>Es war einmal in Amerika</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C174" s="2" t="n"/>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Sidney Lumet</t>
+          <t>Sergio Leone</t>
         </is>
       </c>
       <c r="E174" s="3" t="n">
-        <v>3.92</v>
+        <v>4.22</v>
       </c>
       <c r="F174" s="4" t="n"/>
       <c r="G174" s="5" t="n">
-        <v>189943</v>
+        <v>314152</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>124</v>
+        <v>217</v>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>11.04.2025</t>
+          <t>08.06.2026</t>
         </is>
       </c>
       <c r="J174" s="6" t="inlineStr">
         <is>
-          <t>New York cop Frank Serpico blows the whistle on the rampant corruption in the force only to have his comrades turn against him.</t>
+          <t>A former Prohibition-era Jewish gangster returns to the Lower East Side of Manhattan over thirty years later, where he once again must confront the ghosts and regrets of his old life.</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/serpico-100.html</t>
+          <t>https://www.arte.tv/de/videos/046617-000-A/es-war-einmal-in-amerika/</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/serpico/</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="82" customHeight="1">
+          <t>https://letterboxd.com/film/once-upon-a-time-in-america/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="30" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Ein Kind wie Jake</t>
+          <t>Serpico</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -8874,140 +8874,140 @@
       <c r="C175" s="2" t="n"/>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Silas Howard</t>
+          <t>Sidney Lumet</t>
         </is>
       </c>
       <c r="E175" s="3" t="n">
-        <v>2.94</v>
+        <v>3.92</v>
       </c>
       <c r="F175" s="4" t="n"/>
       <c r="G175" s="5" t="n">
-        <v>3694</v>
+        <v>189943</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>19.08.2025</t>
+          <t>11.04.2025</t>
         </is>
       </c>
       <c r="J175" s="6" t="inlineStr">
         <is>
-          <t>On the eve of the admissions cycle for New York City kindergartens, Alex and Greg Wheeler have high hopes for four-year-old Jake. The director of Jake's preschool encourages them to accentuate Jake's gender expansive behavior to help him stand out. As Alex and Greg navigate their roles as parents, a rift grows between them, one that forces them to confront their own concerns about what's best for Jake, and each other.</t>
+          <t>New York cop Frank Serpico blows the whistle on the rampant corruption in the force only to have his comrades turn against him.</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/ein-kind-wie-jake-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/serpico-100.html</t>
         </is>
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/a-kid-like-jake/</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/serpico/</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="82" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Von uns wird es keiner sein</t>
+          <t>Ein Kind wie Jake</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>ZDF</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C176" s="2" t="n"/>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Simon Ostermann</t>
+          <t>Silas Howard</t>
         </is>
       </c>
       <c r="E176" s="3" t="n">
-        <v>3.32</v>
+        <v>2.94</v>
       </c>
       <c r="F176" s="4" t="n"/>
       <c r="G176" s="5" t="n">
-        <v>374</v>
+        <v>3694</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>03.06.2026</t>
+          <t>19.08.2025</t>
         </is>
       </c>
       <c r="J176" s="6" t="inlineStr">
         <is>
-          <t>An anonymous suicide threat shared on social media causes turmoil at a school. For the students, their parents and the teachers, a race against time begins: who sent the threat? While everyone is on the trail of this question, it turns out that another secret could be involved.</t>
+          <t>On the eve of the admissions cycle for New York City kindergartens, Alex and Greg Wheeler have high hopes for four-year-old Jake. The director of Jake's preschool encourages them to accentuate Jake's gender expansive behavior to help him stand out. As Alex and Greg navigate their roles as parents, a rift grows between them, one that forces them to confront their own concerns about what's best for Jake, and each other.</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/von-uns-wird-es-keiner-sein-movie-100</t>
+          <t>https://www.3sat.de/film/spielfilm/ein-kind-wie-jake-100.html</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/von-uns-wird-es-keiner-sein/</t>
+          <t>https://letterboxd.com/film/a-kid-like-jake/</t>
         </is>
       </c>
     </row>
     <row r="177" ht="56" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Meine Stunden mit Leo</t>
+          <t>Von uns wird es keiner sein</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ZDF</t>
         </is>
       </c>
       <c r="C177" s="2" t="n"/>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Sophie Hyde</t>
+          <t>Simon Ostermann</t>
         </is>
       </c>
       <c r="E177" s="3" t="n">
-        <v>3.62</v>
+        <v>3.32</v>
       </c>
       <c r="F177" s="4" t="n"/>
       <c r="G177" s="5" t="n">
-        <v>91675</v>
+        <v>374</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>28.07.2025</t>
+          <t>03.06.2026</t>
         </is>
       </c>
       <c r="J177" s="6" t="inlineStr">
         <is>
-          <t>Nancy Stokes, a retired schoolteacher, is pretty sure she has never had good sex. Now that her husband has died, she is determined to take a tour of sexual vistas that until now she has only imagined. She even has a plan; it involves an anonymous hotel room, and a sex worker who calls himself Leo Grande.</t>
+          <t>An anonymous suicide threat shared on social media causes turmoil at a school. For the students, their parents and the teachers, a race against time begins: who sent the threat? While everyone is on the trail of this question, it turns out that another secret could be involved.</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/meine-stunden-mit-leo-102.html</t>
+          <t>https://www.zdf.de/filme/von-uns-wird-es-keiner-sein-movie-100</t>
         </is>
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/good-luck-to-you-leo-grande/</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/von-uns-wird-es-keiner-sein/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="56" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Charade</t>
+          <t>Meine Stunden mit Leo</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -9018,284 +9018,284 @@
       <c r="C178" s="2" t="n"/>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Stanley Donen</t>
+          <t>Sophie Hyde</t>
         </is>
       </c>
       <c r="E178" s="3" t="n">
-        <v>4.04</v>
+        <v>3.62</v>
       </c>
       <c r="F178" s="4" t="n"/>
       <c r="G178" s="5" t="n">
-        <v>207824</v>
+        <v>91675</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>21.04.2025</t>
+          <t>28.07.2025</t>
         </is>
       </c>
       <c r="J178" s="6" t="inlineStr">
         <is>
-          <t>After Regina Lampert falls for the dashing Peter Joshua on a skiing holiday in the French Alps, she discovers upon her return to Paris that her husband has been murdered. Soon, she and Peter are giving chase to three of her late husband's World War II cronies, Tex, Scobie and Gideon, who are after a quarter of a million dollars the quartet stole while behind enemy lines.</t>
+          <t>Nancy Stokes, a retired schoolteacher, is pretty sure she has never had good sex. Now that her husband has died, she is determined to take a tour of sexual vistas that until now she has only imagined. She even has a plan; it involves an anonymous hotel room, and a sex worker who calls himself Leo Grande.</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/charade-102.html</t>
+          <t>https://www.3sat.de/film/spielfilm/meine-stunden-mit-leo-102.html</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/charade/</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/good-luck-to-you-leo-grande/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="69" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Into the Beat - Dein Herz tanzt</t>
+          <t>Charade</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>ZDF-tivi</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C179" s="2" t="n"/>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Stefan Westerwelle</t>
+          <t>Stanley Donen</t>
         </is>
       </c>
       <c r="E179" s="3" t="n">
-        <v>2.43</v>
+        <v>4.04</v>
       </c>
       <c r="F179" s="4" t="n"/>
       <c r="G179" s="5" t="n">
-        <v>3902</v>
+        <v>207824</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>30.04.2026</t>
+          <t>21.04.2025</t>
         </is>
       </c>
       <c r="J179" s="6" t="inlineStr">
         <is>
-          <t>Katya is a young, outstanding and upcoming ballet dancer. In just a few weeks she is due to have a major audition for the New York Ballet Academy and Katya has good chances of getting a scholarship. But when she meets a group of street-dancers the girl dives into a completely new world.</t>
+          <t>After Regina Lampert falls for the dashing Peter Joshua on a skiing holiday in the French Alps, she discovers upon her return to Paris that her husband has been murdered. Soon, she and Peter are giving chase to three of her late husband's World War II cronies, Tex, Scobie and Gideon, who are after a quarter of a million dollars the quartet stole while behind enemy lines.</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/into-the-beat---dein-herz-tanzt-movie-100</t>
+          <t>https://www.3sat.de/film/spielfilm/charade-102.html</t>
         </is>
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/into-the-beat/</t>
+          <t>https://letterboxd.com/film/charade/</t>
         </is>
       </c>
     </row>
     <row r="180" ht="56" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Into the Beat - Dein Herz tanzt</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>ZDF-tivi</t>
         </is>
       </c>
       <c r="C180" s="2" t="n"/>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Stephen Gaghan</t>
+          <t>Stefan Westerwelle</t>
         </is>
       </c>
       <c r="E180" s="3" t="n">
-        <v>3.14</v>
+        <v>2.43</v>
       </c>
       <c r="F180" s="4" t="n"/>
       <c r="G180" s="5" t="n">
-        <v>31919</v>
+        <v>3902</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>11.04.2026</t>
+          <t>30.04.2026</t>
         </is>
       </c>
       <c r="J180" s="6" t="inlineStr">
         <is>
-          <t>Kenny Wells, a modern-day prospector, hustler, and dreamer, is desperate for a lucky break. Left with few options, Wells teams up with an equally luckless geologist to execute a grandiose, last-ditch effort: to find gold deep in the uncharted jungle of Indonesia.</t>
+          <t>Katya is a young, outstanding and upcoming ballet dancer. In just a few weeks she is due to have a major audition for the New York Ballet Academy and Katya has good chances of getting a scholarship. But when she meets a group of street-dancers the girl dives into a completely new world.</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/129822-000-A/gold/</t>
+          <t>https://www.zdf.de/filme/into-the-beat---dein-herz-tanzt-movie-100</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/gold-2016/</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/into-the-beat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="56" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Lake Placid</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>ZDFneo</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C181" s="2" t="n"/>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Steve Miner</t>
+          <t>Stephen Gaghan</t>
         </is>
       </c>
       <c r="E181" s="3" t="n">
-        <v>2.77</v>
+        <v>3.14</v>
       </c>
       <c r="F181" s="4" t="n"/>
       <c r="G181" s="5" t="n">
-        <v>59863</v>
+        <v>31919</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>24.06.2026</t>
+          <t>11.04.2026</t>
         </is>
       </c>
       <c r="J181" s="6" t="inlineStr">
         <is>
-          <t>When a man is eaten alive by an unknown creature, the local Game Warden teams up with a paleontologist from New York to find the beast. Add to the mix an eccentric philanthropist with a penchant for "Crocs", and here we go! This quiet, remote lake is suddenly the focus of an intense search for a crocodile with a taste for live animals...and people!</t>
+          <t>Kenny Wells, a modern-day prospector, hustler, and dreamer, is desperate for a lucky break. Left with few options, Wells teams up with an equally luckless geologist to execute a grandiose, last-ditch effort: to find gold deep in the uncharted jungle of Indonesia.</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/lake-placid-movie-100</t>
+          <t>https://www.arte.tv/de/videos/129822-000-A/gold/</t>
         </is>
       </c>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/lake-placid/</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/gold-2016/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="69" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>No Turning Back</t>
+          <t>Lake Placid</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ZDFneo</t>
         </is>
       </c>
       <c r="C182" s="2" t="n"/>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Steven Knight</t>
+          <t>Steve Miner</t>
         </is>
       </c>
       <c r="E182" s="3" t="n">
-        <v>3.6</v>
+        <v>2.77</v>
       </c>
       <c r="F182" s="4" t="n"/>
       <c r="G182" s="5" t="n">
-        <v>169851</v>
+        <v>59863</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>29.03.2026</t>
+          <t>24.06.2026</t>
         </is>
       </c>
       <c r="J182" s="6" t="inlineStr">
         <is>
-          <t>Ivan Locke has worked hard to craft a good life for himself. Tonight, that life will collapse around him. On the eve of the biggest challenge of his career, Ivan receives a phone call that sets in motion a series of events that will unravel his family, job, and soul.</t>
+          <t>When a man is eaten alive by an unknown creature, the local Game Warden teams up with a paleontologist from New York to find the beast. Add to the mix an eccentric philanthropist with a penchant for "Crocs", and here we go! This quiet, remote lake is suddenly the focus of an intense search for a crocodile with a taste for live animals...and people!</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/no-turning-back-100.html</t>
+          <t>https://www.zdf.de/filme/lake-placid-movie-100</t>
         </is>
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/locke/</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="30" customHeight="1">
+          <t>https://letterboxd.com/film/lake-placid/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="56" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Vincent muss sterben</t>
+          <t>No Turning Back</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C183" s="2" t="n"/>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Stéphan Castang</t>
+          <t>Steven Knight</t>
         </is>
       </c>
       <c r="E183" s="3" t="n">
-        <v>3.17</v>
+        <v>3.6</v>
       </c>
       <c r="F183" s="4" t="n"/>
       <c r="G183" s="5" t="n">
-        <v>18237</v>
+        <v>169851</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>29.03.2026</t>
         </is>
       </c>
       <c r="J183" s="6" t="inlineStr">
         <is>
-          <t>Vincent finds himself under attack for no apparent reason overnight. When the phenomenon intensifies, he must run and change his way of life completely.</t>
+          <t>Ivan Locke has worked hard to craft a good life for himself. Tonight, that life will collapse around him. On the eve of the biggest challenge of his career, Ivan receives a phone call that sets in motion a series of events that will unravel his family, job, and soul.</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/120394-000-A/vincent-muss-sterben/</t>
+          <t>https://www.3sat.de/film/spielfilm/no-turning-back-100.html</t>
         </is>
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/vincent-must-die/</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/locke/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="30" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Staying Alive</t>
+          <t>Vincent muss sterben</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -9306,44 +9306,44 @@
       <c r="C184" s="2" t="n"/>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Sylvester Stallone</t>
+          <t>Stéphan Castang</t>
         </is>
       </c>
       <c r="E184" s="3" t="n">
-        <v>2.6</v>
+        <v>3.17</v>
       </c>
       <c r="F184" s="4" t="n"/>
       <c r="G184" s="5" t="n">
-        <v>13883</v>
+        <v>18237</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>25.06.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="J184" s="6" t="inlineStr">
         <is>
-          <t>It's five years later and Tony Manero's Saturday Night Fever is still burning. Now he's strutting toward his biggest challenger yet - making it as a dancer on the Broadway stage.</t>
+          <t>Vincent finds himself under attack for no apparent reason overnight. When the phenomenon intensifies, he must run and change his way of life completely.</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/130330-000-A/staying-alive/</t>
+          <t>https://www.arte.tv/de/videos/120394-000-A/vincent-muss-sterben/</t>
         </is>
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/staying-alive/</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/vincent-must-die/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="43" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Queen of Montreuil</t>
+          <t>Staying Alive</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -9354,44 +9354,44 @@
       <c r="C185" s="2" t="n"/>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Sólveig Anspach</t>
+          <t>Sylvester Stallone</t>
         </is>
       </c>
       <c r="E185" s="3" t="n">
-        <v>3.36</v>
+        <v>2.6</v>
       </c>
       <c r="F185" s="4" t="n"/>
       <c r="G185" s="5" t="n">
-        <v>648</v>
+        <v>13883</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>25.06.2026</t>
         </is>
       </c>
       <c r="J185" s="6" t="inlineStr">
         <is>
-          <t>It's early summer and Agathe is back in France, at home in Montreuil. She has to get over her husband's death and return to her work as a film director. The unexpected arrival at her house of a couple of Icelanders, a sea lion and a neighbour that she has always desired yet never vanquished will give Agathe the strength to get her life back on track...</t>
+          <t>It's five years later and Tony Manero's Saturday Night Fever is still burning. Now he's strutting toward his biggest challenger yet - making it as a dancer on the Broadway stage.</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/128723-000-A/queen-of-montreuil/</t>
+          <t>https://www.arte.tv/de/videos/130330-000-A/staying-alive/</t>
         </is>
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/queen-of-montreuil/</t>
+          <t>https://letterboxd.com/film/staying-alive/</t>
         </is>
       </c>
     </row>
     <row r="186" ht="69" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Der Effekt des Wassers</t>
+          <t>Queen of Montreuil</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -9406,136 +9406,136 @@
         </is>
       </c>
       <c r="E186" s="3" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="F186" s="4" t="n"/>
       <c r="G186" s="5" t="n">
-        <v>1535</v>
+        <v>648</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>09.05.2018</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="J186" s="6" t="inlineStr">
         <is>
-          <t>Samir, a lanky crane operator in Montreuil, falls madly for Agathe. As master swimmer at the pool Thorez he decides to take swimming lessons with her. But the lie does not last three lessons - Agathe hate liars. Chosen to represent the Seine-Saint-Denis, Agathe flies to Iceland for the 10th Congress of the International Masters Swimming. Samir has no choice but to fly in turn also.</t>
+          <t>It's early summer and Agathe is back in France, at home in Montreuil. She has to get over her husband's death and return to her work as a film director. The unexpected arrival at her house of a couple of Icelanders, a sea lion and a neighbour that she has always desired yet never vanquished will give Agathe the strength to get her life back on track...</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/080049-000-A/der-effekt-des-wassers/</t>
+          <t>https://www.arte.tv/de/videos/128723-000-A/queen-of-montreuil/</t>
         </is>
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-together-project/</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="30" customHeight="1">
+          <t>https://letterboxd.com/film/queen-of-montreuil/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="69" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Die Päpstin</t>
+          <t>Der Effekt des Wassers</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>ZDFneo</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C187" s="2" t="n"/>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Sönke Wortmann</t>
+          <t>Sólveig Anspach</t>
         </is>
       </c>
       <c r="E187" s="3" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="F187" s="4" t="n"/>
       <c r="G187" s="5" t="n">
-        <v>3277</v>
+        <v>1535</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>21.06.2026</t>
+          <t>09.05.2018</t>
         </is>
       </c>
       <c r="J187" s="6" t="inlineStr">
         <is>
-          <t>A 9th century woman of English extraction born in the German city of Ingelheim disguises herself as a man and rises through the Vatican ranks.</t>
+          <t>Samir, a lanky crane operator in Montreuil, falls madly for Agathe. As master swimmer at the pool Thorez he decides to take swimming lessons with her. But the lie does not last three lessons - Agathe hate liars. Chosen to represent the Seine-Saint-Denis, Agathe flies to Iceland for the 10th Congress of the International Masters Swimming. Samir has no choice but to fly in turn also.</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/die-paepstin-movie-100</t>
+          <t>https://www.arte.tv/de/videos/080049-000-A/der-effekt-des-wassers/</t>
         </is>
       </c>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/pope-joan-2009/</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/the-together-project/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="30" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Nö</t>
+          <t>Die Päpstin</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ZDFneo</t>
         </is>
       </c>
       <c r="C188" s="2" t="n"/>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Terence Young</t>
+          <t>Sönke Wortmann</t>
         </is>
       </c>
       <c r="E188" s="3" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="F188" s="4" t="n"/>
       <c r="G188" s="5" t="n">
-        <v>234670</v>
+        <v>3277</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>31.05.2025</t>
+          <t>21.06.2026</t>
         </is>
       </c>
       <c r="J188" s="6" t="inlineStr">
         <is>
-          <t>Agent 007 battles mysterious Dr. No, a scientific genius bent on destroying the U.S. space program. As the countdown to disaster begins, Bond must go to Jamaica, where he encounters beautiful Honey Ryder, to confront a megalomaniacal villain in his massive island headquarters.</t>
+          <t>A 9th century woman of English extraction born in the German city of Ingelheim disguises herself as a man and rises through the Vatican ranks.</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/noe-100.html</t>
+          <t>https://www.zdf.de/filme/die-paepstin-movie-100</t>
         </is>
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/dr-no/</t>
+          <t>https://letterboxd.com/film/pope-joan-2009/</t>
         </is>
       </c>
     </row>
     <row r="189" ht="56" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Die Witwe Clicquot</t>
+          <t>Nö</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -9546,145 +9546,145 @@
       <c r="C189" s="2" t="n"/>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Thomas Napper</t>
+          <t>Terence Young</t>
         </is>
       </c>
       <c r="E189" s="3" t="n">
-        <v>3.06</v>
+        <v>3.4</v>
       </c>
       <c r="F189" s="4" t="n"/>
       <c r="G189" s="5" t="n">
-        <v>10607</v>
+        <v>234670</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>04.06.2026</t>
+          <t>31.05.2025</t>
         </is>
       </c>
       <c r="J189" s="6" t="inlineStr">
         <is>
-          <t>After her husband's death, Madame Clicquot flouts convention by assuming the reins of their wine business, defying her critics and ultimately revolutionizing the champagne industry, establishing her as one of the world's first great businesswomen.</t>
+          <t>Agent 007 battles mysterious Dr. No, a scientific genius bent on destroying the U.S. space program. As the countdown to disaster begins, Bond must go to Jamaica, where he encounters beautiful Honey Ryder, to confront a megalomaniacal villain in his massive island headquarters.</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/die-witwe-clicquot-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/noe-100.html</t>
         </is>
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/widow-clicquot/</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="108" customHeight="1">
+          <t>https://letterboxd.com/film/dr-no/</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="56" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Schweigeminute</t>
+          <t>Die Witwe Clicquot</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>ZDF</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C190" s="2" t="n"/>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Thorsten Schmidt</t>
+          <t>Thomas Napper</t>
         </is>
       </c>
       <c r="E190" s="3" t="n">
-        <v>3.31</v>
+        <v>3.06</v>
       </c>
       <c r="F190" s="4" t="n"/>
       <c r="G190" s="5" t="n">
-        <v>293</v>
+        <v>10607</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>04.06.2026</t>
         </is>
       </c>
       <c r="J190" s="6" t="inlineStr">
         <is>
-          <t>The end of a summer, a sleepy fishing port on the Baltic Sea and the beginning of a great feeling that must not be: Shortly before the start of the new school year, the 18-year-old Christian falls in love with his new English teacher Stella Petersen. In a moment of unexpected lightness and freedom, in the dunes and seascape far away from the small town, Stella and Christian discover a shared longing and an attraction to each other, the intensity of which both overwhelmed. But soon after class has begun again, the secret relationship between the young teacher and her pupil threatens the scandal ...</t>
+          <t>After her husband's death, Madame Clicquot flouts convention by assuming the reins of their wine business, defying her critics and ultimately revolutionizing the champagne industry, establishing her as one of the world's first great businesswomen.</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/schweigeminute-movie-100</t>
+          <t>https://www.3sat.de/film/spielfilm/die-witwe-clicquot-100.html</t>
         </is>
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/a-minutes-silence/</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/widow-clicquot/</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="108" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Lola rennt</t>
+          <t>Schweigeminute</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>ZDFneo</t>
+          <t>ZDF</t>
         </is>
       </c>
       <c r="C191" s="2" t="n"/>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Tom Tykwer</t>
+          <t>Thorsten Schmidt</t>
         </is>
       </c>
       <c r="E191" s="3" t="n">
-        <v>3.86</v>
+        <v>3.31</v>
       </c>
       <c r="F191" s="4" t="n"/>
       <c r="G191" s="5" t="n">
-        <v>262849</v>
+        <v>293</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>26.06.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="J191" s="6" t="inlineStr">
         <is>
-          <t>Lola receives a phone call from her boyfriend Manni. He lost 100,000 DM in a subway train that belongs to a very bad guy. She has 20 minutes to raise this amount and meet Manni. Otherwise, he will rob a store to get the money. Three different alternatives may happen depending on some minor event along Lola's run.</t>
+          <t>The end of a summer, a sleepy fishing port on the Baltic Sea and the beginning of a great feeling that must not be: Shortly before the start of the new school year, the 18-year-old Christian falls in love with his new English teacher Stella Petersen. In a moment of unexpected lightness and freedom, in the dunes and seascape far away from the small town, Stella and Christian discover a shared longing and an attraction to each other, the intensity of which both overwhelmed. But soon after class has begun again, the secret relationship between the young teacher and her pupil threatens the scandal ...</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/lola-rennt-movie-100</t>
+          <t>https://www.zdf.de/filme/schweigeminute-movie-100</t>
         </is>
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/run-lola-run/</t>
+          <t>https://letterboxd.com/film/a-minutes-silence/</t>
         </is>
       </c>
     </row>
     <row r="192" ht="56" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Das Parfum - Die Geschichte eines Mörders</t>
+          <t>Lola rennt</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ZDFneo</t>
         </is>
       </c>
       <c r="C192" s="2" t="n"/>
@@ -9694,184 +9694,184 @@
         </is>
       </c>
       <c r="E192" s="3" t="n">
-        <v>3.59</v>
+        <v>3.86</v>
       </c>
       <c r="F192" s="4" t="n"/>
       <c r="G192" s="5" t="n">
-        <v>196934</v>
+        <v>262849</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>141</v>
+        <v>76</v>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>17.10.2025</t>
+          <t>26.06.2026</t>
         </is>
       </c>
       <c r="J192" s="6" t="inlineStr">
         <is>
-          <t>Jean-Baptiste Grenouille, born in the stench of 18th century Paris, develops a superior olfactory sense, which he uses to create the world's finest perfumes. However, his work takes a dark turn as he tries to preserve scents in the search for the ultimate perfume.</t>
+          <t>Lola receives a phone call from her boyfriend Manni. He lost 100,000 DM in a subway train that belongs to a very bad guy. She has 20 minutes to raise this amount and meet Manni. Otherwise, he will rob a store to get the money. Three different alternatives may happen depending on some minor event along Lola's run.</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/das-parfum---die-geschichte-eines-moerders-100.html</t>
+          <t>https://www.zdf.de/filme/lola-rennt-movie-100</t>
         </is>
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/perfume-the-story-of-a-murderer/</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="82" customHeight="1">
+          <t>https://letterboxd.com/film/run-lola-run/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="56" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Das Parfum - Die Geschichte eines Mörders</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>ZDF</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C193" s="2" t="n"/>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Ulli Lommel</t>
+          <t>Tom Tykwer</t>
         </is>
       </c>
       <c r="E193" s="3" t="n">
-        <v>3.05</v>
+        <v>3.59</v>
       </c>
       <c r="F193" s="4" t="n"/>
       <c r="G193" s="5" t="n">
-        <v>2368</v>
+        <v>196934</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>17.10.2025</t>
         </is>
       </c>
       <c r="J193" s="6" t="inlineStr">
         <is>
-          <t>Nightmares of the past haunt the beautiful, mysterious Olivia, a London resident who begins a passionate affair with American businessman Mike. Trapped in a loveless marriage and traumatized by memories of her mother's brutal murder, Olivia hopes her lover will offer a chance at a new life. However, ghostly voices and brutal murders ignite a fiendish, twist-filled story of double identities, deception, and erotic terror.</t>
+          <t>Jean-Baptiste Grenouille, born in the stench of 18th century Paris, develops a superior olfactory sense, which he uses to create the world's finest perfumes. However, his work takes a dark turn as he tries to preserve scents in the search for the ultimate perfume.</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>https://www.zdf.de/filme/olivia-movie-100</t>
+          <t>https://www.3sat.de/film/spielfilm/das-parfum---die-geschichte-eines-moerders-100.html</t>
         </is>
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/olivia-1983/</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/perfume-the-story-of-a-murderer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="82" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Notre Dame - Die Liebe ist eine Baustelle</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>ZDF</t>
         </is>
       </c>
       <c r="C194" s="2" t="n"/>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Valérie Donzelli</t>
+          <t>Ulli Lommel</t>
         </is>
       </c>
       <c r="E194" s="3" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="F194" s="4" t="n"/>
       <c r="G194" s="5" t="n">
-        <v>1562</v>
+        <v>2368</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>01.04.2026</t>
+          <t>15.05.2026</t>
         </is>
       </c>
       <c r="J194" s="6" t="inlineStr">
         <is>
-          <t>Maud is an architect and a mother. Due to a misunderstanding, she wins the competition to refurbish the parvis of Notre-Dame. Torn between these responsibilities and love issues, she will go through an emotional storm.</t>
+          <t>Nightmares of the past haunt the beautiful, mysterious Olivia, a London resident who begins a passionate affair with American businessman Mike. Trapped in a loveless marriage and traumatized by memories of her mother's brutal murder, Olivia hopes her lover will offer a chance at a new life. However, ghostly voices and brutal murders ignite a fiendish, twist-filled story of double identities, deception, and erotic terror.</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/129910-000-A/notre-dame-die-liebe-ist-eine-baustelle/</t>
+          <t>https://www.zdf.de/filme/olivia-movie-100</t>
         </is>
       </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/notre-dame/</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="30" customHeight="1">
+          <t>https://letterboxd.com/film/olivia-1983/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="43" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Notre Dame - Die Liebe ist eine Baustelle</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C195" s="2" t="n"/>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Vicky Jewson</t>
+          <t>Valérie Donzelli</t>
         </is>
       </c>
       <c r="E195" s="3" t="n">
-        <v>2.58</v>
+        <v>2.98</v>
       </c>
       <c r="F195" s="4" t="n"/>
       <c r="G195" s="5" t="n">
-        <v>13235</v>
+        <v>1562</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>22.03.2025</t>
+          <t>01.04.2026</t>
         </is>
       </c>
       <c r="J195" s="6" t="inlineStr">
         <is>
-          <t>A counter-terrorism expert takes a job protecting a young heiress. After an attempted kidnapping puts both of their lives in danger, they must flee.</t>
+          <t>Maud is an architect and a mother. Due to a misunderstanding, she wins the competition to refurbish the parvis of Notre-Dame. Torn between these responsibilities and love issues, she will go through an emotional storm.</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/close-100.html</t>
+          <t>https://www.arte.tv/de/videos/129910-000-A/notre-dame-die-liebe-ist-eine-baustelle/</t>
         </is>
       </c>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/close-2019/</t>
+          <t>https://letterboxd.com/film/notre-dame/</t>
         </is>
       </c>
     </row>
     <row r="196" ht="30" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Die Blechtrommel</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -9882,94 +9882,94 @@
       <c r="C196" s="2" t="n"/>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Volker Schlöndorff</t>
+          <t>Vicky Jewson</t>
         </is>
       </c>
       <c r="E196" s="3" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="F196" s="4" t="n">
-        <v>4</v>
-      </c>
+        <v>2.58</v>
+      </c>
+      <c r="F196" s="4" t="n"/>
       <c r="G196" s="5" t="n">
-        <v>21900</v>
+        <v>13235</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>09.05.2025</t>
+          <t>22.03.2025</t>
         </is>
       </c>
       <c r="J196" s="6" t="inlineStr">
         <is>
-          <t>In 1924, Oskar Matzerath is born in the Free City of Danzig. At age three, he falls down a flight of stairs and stops growing. In 1939, World War II breaks out.</t>
+          <t>A counter-terrorism expert takes a job protecting a young heiress. After an attempted kidnapping puts both of their lives in danger, they must flee.</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/die-blechtrommel-100.html</t>
+          <t>https://www.3sat.de/film/spielfilm/close-100.html</t>
         </is>
       </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-tin-drum/</t>
+          <t>https://letterboxd.com/film/close-2019/</t>
         </is>
       </c>
     </row>
     <row r="197" ht="30" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Rosalie</t>
+          <t>Die Blechtrommel</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>ARTE.DE</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C197" s="2" t="n"/>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>W.S. Van Dyke</t>
+          <t>Volker Schlöndorff</t>
         </is>
       </c>
       <c r="E197" s="3" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="F197" s="4" t="n"/>
+        <v>3.72</v>
+      </c>
+      <c r="F197" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="G197" s="5" t="n">
-        <v>225</v>
+        <v>21900</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>24.06.2026</t>
+          <t>09.05.2025</t>
         </is>
       </c>
       <c r="J197" s="6" t="inlineStr">
         <is>
-          <t>West Point cadet Dick Thorpe falls in love with a girl, who turns out to be a princess from an European kingdom.</t>
+          <t>In 1924, Oskar Matzerath is born in the Free City of Danzig. At age three, he falls down a flight of stairs and stops growing. In 1939, World War II breaks out.</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/125582-000-A/rosalie/</t>
+          <t>https://www.3sat.de/film/spielfilm/die-blechtrommel-100.html</t>
         </is>
       </c>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/rosalie/</t>
+          <t>https://letterboxd.com/film/the-tin-drum/</t>
         </is>
       </c>
     </row>
     <row r="198" ht="30" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Bis dann, mein Sohn</t>
+          <t>Rosalie</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -9980,236 +9980,236 @@
       <c r="C198" s="2" t="n"/>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Wang Xiaoshuai</t>
+          <t>W.S. Van Dyke</t>
         </is>
       </c>
       <c r="E198" s="3" t="n">
-        <v>4.16</v>
+        <v>3.18</v>
       </c>
       <c r="F198" s="4" t="n"/>
       <c r="G198" s="5" t="n">
-        <v>15573</v>
+        <v>225</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>174</v>
+        <v>108</v>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>19.09.2022</t>
+          <t>24.06.2026</t>
         </is>
       </c>
       <c r="J198" s="6" t="inlineStr">
         <is>
-          <t>Two married couples adjust to the vast social and economic changes taking place in China from the 1980s to the present.</t>
+          <t>West Point cadet Dick Thorpe falls in love with a girl, who turns out to be a princess from an European kingdom.</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>https://www.arte.tv/de/videos/105513-000-A/bis-dann-mein-sohn/</t>
+          <t>https://www.arte.tv/de/videos/125582-000-A/rosalie/</t>
         </is>
       </c>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/so-long-my-son/</t>
-        </is>
-      </c>
-    </row>
-    <row r="199" ht="43" customHeight="1">
+          <t>https://letterboxd.com/film/rosalie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="30" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Meine chaotische Hochzeit</t>
+          <t>Bis dann, mein Sohn</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARTE.DE</t>
         </is>
       </c>
       <c r="C199" s="2" t="n"/>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Wayne Blair</t>
+          <t>Wang Xiaoshuai</t>
         </is>
       </c>
       <c r="E199" s="3" t="n">
-        <v>3.24</v>
+        <v>4.16</v>
       </c>
       <c r="F199" s="4" t="n"/>
       <c r="G199" s="5" t="n">
-        <v>2996</v>
+        <v>15573</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>97</v>
+        <v>174</v>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>10.06.2025</t>
+          <t>19.09.2022</t>
         </is>
       </c>
       <c r="J199" s="6" t="inlineStr">
         <is>
-          <t>Lauren and Ned are engaged, they are in love, and they have just ten days to find Lauren’s mother who has gone AWOL somewhere in the remote far north of Australia, reunite her parents and pull off their dream wedding.</t>
+          <t>Two married couples adjust to the vast social and economic changes taking place in China from the 1980s to the present.</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/meine-chaotische-hochzeit-100.html</t>
+          <t>https://www.arte.tv/de/videos/105513-000-A/bis-dann-mein-sohn/</t>
         </is>
       </c>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/top-end-wedding/</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="56" customHeight="1">
+          <t>https://letterboxd.com/film/so-long-my-son/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="43" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Im weißen Rössl</t>
+          <t>Meine chaotische Hochzeit</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>ARD</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C200" s="2" t="n"/>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Werner Jacobs</t>
+          <t>Wayne Blair</t>
         </is>
       </c>
       <c r="E200" s="3" t="n">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="F200" s="4" t="n"/>
       <c r="G200" s="5" t="n">
-        <v>437</v>
+        <v>2996</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>06.06.2026</t>
+          <t>10.06.2025</t>
         </is>
       </c>
       <c r="J200" s="6" t="inlineStr">
         <is>
-          <t>Leopold, head waiter at the "Weißen Rössl" (White Horse Inn), is secretly in love with the owner of the restaurant, Josepha. But she's only interested in the lawyer Dr. Siedler. Jealous, Leopold comes up with a plan to gain Josepha's attention.</t>
+          <t>Lauren and Ned are engaged, they are in love, and they have just ten days to find Lauren’s mother who has gone AWOL somewhere in the remote far north of Australia, reunite her parents and pull off their dream wedding.</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS9wbGFuQVJEX2U2OGU2ODg5LWY2OTMtNGRkYy05NWMzLTc3MGI2ZmY5ODVmN19nYW56ZVNlbmR1bmc</t>
+          <t>https://www.3sat.de/film/spielfilm/meine-chaotische-hochzeit-100.html</t>
         </is>
       </c>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/the-white-horse-inn-1960/</t>
+          <t>https://letterboxd.com/film/top-end-wedding/</t>
         </is>
       </c>
     </row>
     <row r="201" ht="56" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Jericho Ridge - Unter Beschuss</t>
+          <t>Im weißen Rössl</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARD</t>
         </is>
       </c>
       <c r="C201" s="2" t="n"/>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Will Gilbey</t>
+          <t>Werner Jacobs</t>
         </is>
       </c>
       <c r="E201" s="3" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="F201" s="4" t="n"/>
       <c r="G201" s="5" t="n">
-        <v>1823</v>
+        <v>437</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>24.02.2025</t>
+          <t>06.06.2026</t>
         </is>
       </c>
       <c r="J201" s="6" t="inlineStr">
         <is>
-          <t>North Washington county sheriff Tabby finds herself alone in the sheriff’s office one night while her colleagues are out on patrol, but she soon finds out they’ve been set up by a murderous drug cartel while she herself comes under siege at the office, where she must battle desperately to save herself and her son.</t>
+          <t>Leopold, head waiter at the "Weißen Rössl" (White Horse Inn), is secretly in love with the owner of the restaurant, Josepha. But she's only interested in the lawyer Dr. Siedler. Jealous, Leopold comes up with a plan to gain Josepha's attention.</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/jericho-ridge---unter-beschuss-100.html</t>
+          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS9wbGFuQVJEX2U2OGU2ODg5LWY2OTMtNGRkYy05NWMzLTc3MGI2ZmY5ODVmN19nYW56ZVNlbmR1bmc</t>
         </is>
       </c>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/jericho-ridge/</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="69" customHeight="1">
+          <t>https://letterboxd.com/film/the-white-horse-inn-1960/</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="56" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Enkel für Anfänger</t>
+          <t>Jericho Ridge - Unter Beschuss</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>ARD</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C202" s="2" t="n"/>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Wolfgang Groos</t>
+          <t>Will Gilbey</t>
         </is>
       </c>
       <c r="E202" s="3" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="F202" s="4" t="n"/>
       <c r="G202" s="5" t="n">
-        <v>836</v>
+        <v>1823</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>27.06.2026</t>
+          <t>24.02.2025</t>
         </is>
       </c>
       <c r="J202" s="6" t="inlineStr">
         <is>
-          <t>Retirees Karin, Gerhard and Philippa are not in the mood for Nordic walking and seniors' courses at the university. When Philippa, who is living life to the full as Leonie's godmother, helps the two to unexpected grandparenthood, they suddenly have two "lively" god-grandchildren to look after, a huge bouncy castle standing in the garden and Lego bricks stuck to their feet.</t>
+          <t>North Washington county sheriff Tabby finds herself alone in the sheriff’s office one night while her colleagues are out on patrol, but she soon finds out they’ve been set up by a murderous drug cartel while she herself comes under siege at the office, where she must battle desperately to save herself and her son.</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS9wbGFuQVJEXzA4NTc3NDVlLTAxZTctNDJiZC1hMGI0LTEzZjE1ZGNiZGY3N19nYW56ZVNlbmR1bmc</t>
+          <t>https://www.3sat.de/film/spielfilm/jericho-ridge---unter-beschuss-100.html</t>
         </is>
       </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/granny-nanny/</t>
+          <t>https://letterboxd.com/film/jericho-ridge/</t>
         </is>
       </c>
     </row>
     <row r="203" ht="69" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Match Point</t>
+          <t>Enkel für Anfänger</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -10220,37 +10220,37 @@
       <c r="C203" s="2" t="n"/>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Woody Allen</t>
+          <t>Wolfgang Groos</t>
         </is>
       </c>
       <c r="E203" s="3" t="n">
-        <v>3.64</v>
+        <v>3.15</v>
       </c>
       <c r="F203" s="4" t="n"/>
       <c r="G203" s="5" t="n">
-        <v>179210</v>
+        <v>836</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>26.06.2026</t>
+          <t>27.06.2026</t>
         </is>
       </c>
       <c r="J203" s="6" t="inlineStr">
         <is>
-          <t>Chris, a former tennis pro, takes a job as an instructor and befriends his wealthy young student, Tom. After being introduced to his family, Chris is soon engaged to Tom's sister, Chloe. Despite the professional and financial advantages that this relationship affords him, Chris becomes obsessed with Tom's fiancee, American actress Nola.</t>
+          <t>Retirees Karin, Gerhard and Philippa are not in the mood for Nordic walking and seniors' courses at the university. When Philippa, who is living life to the full as Leonie's godmother, helps the two to unexpected grandparenthood, they suddenly have two "lively" god-grandchildren to look after, a huge bouncy castle standing in the garden and Lego bricks stuck to their feet.</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
-          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS8zZTIyZjM4OC1jMDRhLTRkOTEtYTBhMC0zNDRmNWMzZTQ5ZDJfZ2FuemVTZW5kdW5n</t>
+          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS9wbGFuQVJEXzA4NTc3NDVlLTAxZTctNDJiZC1hMGI0LTEzZjE1ZGNiZGY3N19nYW56ZVNlbmR1bmc</t>
         </is>
       </c>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/match-point/</t>
+          <t>https://letterboxd.com/film/granny-nanny/</t>
         </is>
       </c>
     </row>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARD</t>
         </is>
       </c>
       <c r="C204" s="2" t="n"/>
@@ -10293,7 +10293,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>https://www.3sat.de/film/spielfilm/match-point-100.html</t>
+          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS8zZTIyZjM4OC1jMDRhLTRkOTEtYTBhMC0zNDRmNWMzZTQ5ZDJfZ2FuemVTZW5kdW5n</t>
         </is>
       </c>
       <c r="L204" s="2" t="inlineStr">
@@ -10302,32 +10302,32 @@
         </is>
       </c>
     </row>
-    <row r="205" ht="56" customHeight="1">
+    <row r="205" ht="69" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>À la Carte! - Freiheit geht durch den Magen</t>
+          <t>Match Point</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>ARD</t>
+          <t>3Sat</t>
         </is>
       </c>
       <c r="C205" s="2" t="n"/>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Éric Besnard</t>
+          <t>Woody Allen</t>
         </is>
       </c>
       <c r="E205" s="3" t="n">
-        <v>3.31</v>
+        <v>3.64</v>
       </c>
       <c r="F205" s="4" t="n"/>
       <c r="G205" s="5" t="n">
-        <v>10281</v>
+        <v>179210</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
@@ -10336,29 +10336,29 @@
       </c>
       <c r="J205" s="6" t="inlineStr">
         <is>
-          <t>France, 1789 - just before the Revolution. When talented chef Manceron is dismissed from his prestigious position by the Duke of Chamfort, he loses the taste for cooking. But when he meets the mysterious Louise, together they decide to create the very first restaurant in France.</t>
+          <t>Chris, a former tennis pro, takes a job as an instructor and befriends his wealthy young student, Tom. After being introduced to his family, Chris is soon engaged to Tom's sister, Chloe. Despite the professional and financial advantages that this relationship affords him, Chris becomes obsessed with Tom's fiancee, American actress Nola.</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
-          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS9wbGFuQVJEX2ZhZWZmZWY2LTNmZDItNDIyOS04NDRiLTAwOWU4MDQ2NjYxZl9nYW56ZVNlbmR1bmc</t>
+          <t>https://www.3sat.de/film/spielfilm/match-point-100.html</t>
         </is>
       </c>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>https://letterboxd.com/film/delicious-2021/</t>
+          <t>https://letterboxd.com/film/match-point/</t>
         </is>
       </c>
     </row>
     <row r="206" ht="56" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>À la Carte! – Freiheit geht durch den Magen</t>
+          <t>À la Carte! - Freiheit geht durch den Magen</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>3Sat</t>
+          <t>ARD</t>
         </is>
       </c>
       <c r="C206" s="2" t="n"/>
@@ -10379,20 +10379,68 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
+          <t>26.06.2026</t>
+        </is>
+      </c>
+      <c r="J206" s="6" t="inlineStr">
+        <is>
+          <t>France, 1789 - just before the Revolution. When talented chef Manceron is dismissed from his prestigious position by the Duke of Chamfort, he loses the taste for cooking. But when he meets the mysterious Louise, together they decide to create the very first restaurant in France.</t>
+        </is>
+      </c>
+      <c r="K206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ardmediathek.de/video/Y3JpZDovL2FyZC5kZS9wbGFuQVJEX2ZhZWZmZWY2LTNmZDItNDIyOS04NDRiLTAwOWU4MDQ2NjYxZl9nYW56ZVNlbmR1bmc</t>
+        </is>
+      </c>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/delicious-2021/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="56" customHeight="1">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>À la Carte! – Freiheit geht durch den Magen</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>3Sat</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="n"/>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Éric Besnard</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="F207" s="4" t="n"/>
+      <c r="G207" s="5" t="n">
+        <v>10281</v>
+      </c>
+      <c r="H207" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
           <t>08.02.2026</t>
         </is>
       </c>
-      <c r="J206" s="6" t="inlineStr">
+      <c r="J207" s="6" t="inlineStr">
         <is>
           <t>France, 1789 - just before the Revolution. When talented chef Manceron is dismissed from his prestigious position by the Duke of Chamfort, he loses the taste for cooking. But when he meets the mysterious Louise, together they decide to create the very first restaurant in France.</t>
         </is>
       </c>
-      <c r="K206" s="2" t="inlineStr">
+      <c r="K207" s="2" t="inlineStr">
         <is>
           <t>https://www.3sat.de/film/spielfilm/-la-carte---freiheit-geht-durch-den-magen-100.html</t>
         </is>
       </c>
-      <c r="L206" s="2" t="inlineStr">
+      <c r="L207" s="2" t="inlineStr">
         <is>
           <t>https://letterboxd.com/film/delicious-2021/</t>
         </is>
